--- a/logs/final_winner_optimization/Final_winner_optimization.xlsx
+++ b/logs/final_winner_optimization/Final_winner_optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/final_winner_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDBAFD9A-C14A-499A-8E4F-BE04E5D348F3}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B45ABE83-0528-454B-B1FE-0988A4535BE6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="147">
   <si>
     <t>date</t>
   </si>
@@ -462,6 +462,15 @@
   <si>
     <t>[0.1, 0.001]</t>
   </si>
+  <si>
+    <t>03-01_07-25-54_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
+  <si>
+    <t>03-01_14-15-43_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
+  <si>
+    <t>03-01_22-01-05_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -605,13 +614,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46082.448245254629" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="36" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46083.419104976849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="39" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-01T02:11:27"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-01T22:01:05"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -743,28 +752,28 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.30180636938325411" maxValue="0.85581484240928529"/>
     </cacheField>
     <cacheField name="Val Global Closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.35402920390919479" maxValue="0.28983463219748351"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.92529463933909406" maxValue="0.28983463219748351"/>
     </cacheField>
     <cacheField name="step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.8011894210072" maxValue="41.819716031652987"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.27469651451409" maxValue="41.819716031652987"/>
     </cacheField>
     <cacheField name="step R2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.31833894414921388" maxValue="0.85194307226105237"/>
     </cacheField>
     <cacheField name="local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.8011894210072" maxValue="41.819716031652987"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.27469651451409" maxValue="41.819716031652987"/>
     </cacheField>
     <cacheField name="global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.8011894210072" maxValue="1336954740649870"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="11.27469651451409" maxValue="1336954740649870"/>
     </cacheField>
     <cacheField name="global open R2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.31833894414921388" maxValue="0.85194307226105237"/>
     </cacheField>
     <cacheField name="global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="69.623397543544598" maxValue="152.46633963909221"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="69.623397543544598" maxValue="169.06649342462879"/>
     </cacheField>
     <cacheField name="global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.84376231738702545" maxValue="0.28570443944854401"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.84376231738702545" maxValue="0.30732203056010721"/>
     </cacheField>
     <cacheField name="recursivity" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.8" maxValue="0.8"/>
@@ -788,25 +797,25 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.1638333701615338E-2" maxValue="0.77593170988192284"/>
     </cacheField>
     <cacheField name="Surge Velocity Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.4559220538329798E-2" maxValue="0.57571505934527367"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.3364344705318723E-2" maxValue="0.57571505934527367"/>
     </cacheField>
     <cacheField name="Surge Velocity Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.1804357065468198" maxValue="0.53121658649646997"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.1804357065468198" maxValue="0.53989292996903793"/>
     </cacheField>
     <cacheField name="Sway Velocity Step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.7176934265066139E-2" maxValue="0.13315021487110809"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.6143628429398661E-2" maxValue="0.13315021487110809"/>
     </cacheField>
     <cacheField name="Sway Velocity Step R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.53866294396224468" maxValue="0.90583772727581424"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.53866294396224468" maxValue="0.90941791130086391"/>
     </cacheField>
     <cacheField name="Sway Velocity Local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.7176934265066139E-2" maxValue="0.13315021487110809"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.6143628429398661E-2" maxValue="0.13315021487110809"/>
     </cacheField>
     <cacheField name="Sway Velocity Global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.7176934265066139E-2" maxValue="0.13315021487110809"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.6143628429398661E-2" maxValue="0.13315021487110809"/>
     </cacheField>
     <cacheField name="Sway Velocity Global open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.53866294396224468" maxValue="0.90583772727581424"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.53866294396224468" maxValue="0.90941791130086391"/>
     </cacheField>
     <cacheField name="Sway Velocity Global closed MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.8366126878513024E-2" maxValue="0.32777690362774559"/>
@@ -830,31 +839,31 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.1798672964141548" maxValue="0.88223633777583421"/>
     </cacheField>
     <cacheField name="Yaw Rate Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.7146057190884668E-2" maxValue="0.28468735236755471"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.7146057190884668E-2" maxValue="0.29538004849098981"/>
     </cacheField>
     <cacheField name="Yaw Rate Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.142929672603894" maxValue="0.65013614484248694"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.18585746541933429" maxValue="0.65013614484248694"/>
     </cacheField>
     <cacheField name="Yaw Angle Step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="47.074901421961002" maxValue="166.84961170860629"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45.004347765404759" maxValue="166.84961170860629"/>
     </cacheField>
     <cacheField name="Yaw Angle Step R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.52511659288826185" maxValue="0.86601653220654784"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.52511659288826185" maxValue="0.87190969290955456"/>
     </cacheField>
     <cacheField name="Yaw Angle Local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="47.074901421961002" maxValue="166.84961170860629"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45.004347765404759" maxValue="166.84961170860629"/>
     </cacheField>
     <cacheField name="Yaw Angle Global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="47.074901421961002" maxValue="166.84961170860629"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45.004347765404759" maxValue="166.84961170860629"/>
     </cacheField>
     <cacheField name="Yaw Angle Global open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.52511659288826185" maxValue="0.86601653220654784"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.52511659288826185" maxValue="0.87190969290955456"/>
     </cacheField>
     <cacheField name="Yaw Angle Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="278.00904088934652" maxValue="608.89575060316417"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="278.00904088934652" maxValue="675.40208085763709"/>
     </cacheField>
     <cacheField name="Yaw Angle Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.73302464213870855" maxValue="0.20873726229601061"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.92231338175471733" maxValue="0.20873726229601061"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -866,7 +875,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="36">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="39">
   <r>
     <d v="2026-02-16T18:21:04"/>
     <s v="02-16_18-21-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
@@ -3639,12 +3648,243 @@
     <n v="378.37002811003902"/>
     <n v="-7.6907798932511984E-2"/>
   </r>
+  <r>
+    <d v="2026-03-01T07:25:54"/>
+    <s v="03-01_07-25-54_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="7.6927538340747018E-2"/>
+    <n v="8.6997805293031405"/>
+    <n v="0.85315970293576116"/>
+    <n v="0.28089806133461392"/>
+    <n v="11.27469651451409"/>
+    <n v="0.8503017121725901"/>
+    <n v="11.27469651451409"/>
+    <n v="11.27469651451409"/>
+    <n v="0.8503017121725901"/>
+    <n v="80.660457277380743"/>
+    <n v="0.30732203056010721"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="3.2630745464777511E-2"/>
+    <n v="0.76305859772483908"/>
+    <n v="3.2630745464777511E-2"/>
+    <n v="3.2630745464777511E-2"/>
+    <n v="0.76305859772483908"/>
+    <n v="6.3364344705318723E-2"/>
+    <n v="0.53989292996903793"/>
+    <n v="2.6143628429398661E-2"/>
+    <n v="0.90941791130086391"/>
+    <n v="2.6143628429398661E-2"/>
+    <n v="2.6143628429398661E-2"/>
+    <n v="0.90941791130086391"/>
+    <n v="0.21707899283722051"/>
+    <n v="0.24786765398682961"/>
+    <n v="3.5663918757243618E-2"/>
+    <n v="0.85682064675510383"/>
+    <n v="3.5663918757243618E-2"/>
+    <n v="3.5663918757243618E-2"/>
+    <n v="0.85682064675510383"/>
+    <n v="0.15977095995904991"/>
+    <n v="0.35857013162338802"/>
+    <n v="45.004347765404759"/>
+    <n v="0.87190969290955456"/>
+    <n v="45.004347765404759"/>
+    <n v="45.004347765404759"/>
+    <n v="0.87190969290955456"/>
+    <n v="322.20161481202211"/>
+    <n v="8.2957406661170907E-2"/>
+  </r>
+  <r>
+    <d v="2026-03-01T14:15:43"/>
+    <s v="03-01_14-15-43_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="8.644082322644582E-2"/>
+    <n v="9.1869195750712009"/>
+    <n v="0.81424238599217835"/>
+    <n v="-0.4376571909467491"/>
+    <n v="12.705586239378309"/>
+    <n v="0.8194384355382428"/>
+    <n v="12.705586239378309"/>
+    <n v="12.705586239378309"/>
+    <n v="0.8194384355382428"/>
+    <n v="110.37526131671351"/>
+    <n v="-0.34391961643249608"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="4.4795238792550887E-2"/>
+    <n v="0.67472864797972332"/>
+    <n v="4.4795238792550887E-2"/>
+    <n v="4.4795238792550887E-2"/>
+    <n v="0.67472864797972332"/>
+    <n v="0.25848561526706332"/>
+    <n v="-0.87693977802150402"/>
+    <n v="2.9750587395985351E-2"/>
+    <n v="0.89692056886319005"/>
+    <n v="2.9750587395985351E-2"/>
+    <n v="2.9750587395985351E-2"/>
+    <n v="0.89692056886319005"/>
+    <n v="0.30557079131078307"/>
+    <n v="-5.8737527467805251E-2"/>
+    <n v="3.7254323423080327E-2"/>
+    <n v="0.85043567506979478"/>
+    <n v="3.7254323423080327E-2"/>
+    <n v="3.7254323423080327E-2"/>
+    <n v="0.85043567506979478"/>
+    <n v="0.29538004849098981"/>
+    <n v="-0.18585746541933429"/>
+    <n v="50.710544807901407"/>
+    <n v="0.85566885024026373"/>
+    <n v="50.710544807901407"/>
+    <n v="50.710544807901407"/>
+    <n v="0.85566885024026373"/>
+    <n v="440.64160881178668"/>
+    <n v="-0.25414369482134958"/>
+  </r>
+  <r>
+    <d v="2026-03-01T22:01:05"/>
+    <s v="03-01_22-01-05_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="7.9983415010330086E-2"/>
+    <n v="12.272633372581399"/>
+    <n v="0.8348849815197108"/>
+    <n v="-0.92529463933909406"/>
+    <n v="23.957640498508209"/>
+    <n v="0.79088617530242744"/>
+    <n v="23.957640498508209"/>
+    <n v="23.957640498508209"/>
+    <n v="0.79088617530242744"/>
+    <n v="169.06649342462879"/>
+    <n v="-0.75504858565799149"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="3.5541332828741307E-2"/>
+    <n v="0.74192397019368572"/>
+    <n v="3.5541332828741307E-2"/>
+    <n v="3.5541332828741307E-2"/>
+    <n v="0.74192397019368572"/>
+    <n v="0.53223992353191174"/>
+    <n v="-2.86475000899387"/>
+    <n v="3.3017654948118882E-2"/>
+    <n v="0.88560087758190476"/>
+    <n v="3.3017654948118882E-2"/>
+    <n v="3.3017654948118882E-2"/>
+    <n v="0.88560087758190476"/>
+    <n v="0.17885269191039929"/>
+    <n v="0.38031362224804671"/>
+    <n v="4.771494460530553E-2"/>
+    <n v="0.80843958973756636"/>
+    <n v="4.771494460530553E-2"/>
+    <n v="4.771494460530553E-2"/>
+    <n v="0.80843958973756636"/>
+    <n v="0.15280022543805241"/>
+    <n v="0.38655542586858582"/>
+    <n v="95.714288061650677"/>
+    <n v="0.72758026369655293"/>
+    <n v="95.714288061650677"/>
+    <n v="95.714288061650677"/>
+    <n v="0.72758026369655293"/>
+    <n v="675.40208085763709"/>
+    <n v="-0.92231338175471733"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24326305-70A8-4C78-9FE9-6DC3DEA8AA33}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:L55" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A1:L58" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -3761,7 +4001,7 @@
     <field x="30"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="54">
+  <rowItems count="57">
     <i>
       <x/>
     </i>
@@ -3876,6 +4116,15 @@
     <i r="3">
       <x/>
     </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x v="3"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
@@ -3989,7 +4238,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW37" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW40" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <tableColumns count="75">
     <tableColumn id="1" xr3:uid="{E29847FD-796C-4D7F-957B-1B478BBCCC1D}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{AFC0F8DD-B9EA-4787-891C-59254C048BBB}" name="model_id"/>
@@ -4334,7 +4583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW37"/>
+  <dimension ref="A1:BW40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="42" max="42" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -12630,6 +12879,678 @@
       </c>
       <c r="BW37">
         <v>-7.6907798932511984E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46082.309652777767</v>
+      </c>
+      <c r="B38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38">
+        <v>16590</v>
+      </c>
+      <c r="G38">
+        <v>4.5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s">
+        <v>79</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>80</v>
+      </c>
+      <c r="M38" t="s">
+        <v>81</v>
+      </c>
+      <c r="N38" t="s">
+        <v>82</v>
+      </c>
+      <c r="O38" t="s">
+        <v>82</v>
+      </c>
+      <c r="P38" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>84</v>
+      </c>
+      <c r="R38">
+        <v>3</v>
+      </c>
+      <c r="S38" t="s">
+        <v>85</v>
+      </c>
+      <c r="T38" t="s">
+        <v>86</v>
+      </c>
+      <c r="U38" t="s">
+        <v>87</v>
+      </c>
+      <c r="V38" t="s">
+        <v>88</v>
+      </c>
+      <c r="W38" t="s">
+        <v>89</v>
+      </c>
+      <c r="X38" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z38">
+        <v>4000</v>
+      </c>
+      <c r="AA38">
+        <v>4000</v>
+      </c>
+      <c r="AC38">
+        <v>512</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE38">
+        <v>0.15</v>
+      </c>
+      <c r="AF38">
+        <v>180</v>
+      </c>
+      <c r="AG38">
+        <v>60</v>
+      </c>
+      <c r="AH38">
+        <v>120</v>
+      </c>
+      <c r="AI38">
+        <v>7.6927538340747018E-2</v>
+      </c>
+      <c r="AJ38">
+        <v>8.6997805293031405</v>
+      </c>
+      <c r="AK38">
+        <v>0.85315970293576116</v>
+      </c>
+      <c r="AL38">
+        <v>0.28089806133461392</v>
+      </c>
+      <c r="AM38">
+        <v>11.27469651451409</v>
+      </c>
+      <c r="AN38">
+        <v>0.8503017121725901</v>
+      </c>
+      <c r="AO38">
+        <v>11.27469651451409</v>
+      </c>
+      <c r="AP38">
+        <v>11.27469651451409</v>
+      </c>
+      <c r="AQ38">
+        <v>0.8503017121725901</v>
+      </c>
+      <c r="AR38">
+        <v>80.660457277380743</v>
+      </c>
+      <c r="AS38">
+        <v>0.30732203056010721</v>
+      </c>
+      <c r="AT38">
+        <v>0.8</v>
+      </c>
+      <c r="AU38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV38">
+        <v>3.2630745464777511E-2</v>
+      </c>
+      <c r="AW38">
+        <v>0.76305859772483908</v>
+      </c>
+      <c r="AX38">
+        <v>3.2630745464777511E-2</v>
+      </c>
+      <c r="AY38">
+        <v>3.2630745464777511E-2</v>
+      </c>
+      <c r="AZ38">
+        <v>0.76305859772483908</v>
+      </c>
+      <c r="BA38">
+        <v>6.3364344705318723E-2</v>
+      </c>
+      <c r="BB38">
+        <v>0.53989292996903793</v>
+      </c>
+      <c r="BC38">
+        <v>2.6143628429398661E-2</v>
+      </c>
+      <c r="BD38">
+        <v>0.90941791130086391</v>
+      </c>
+      <c r="BE38">
+        <v>2.6143628429398661E-2</v>
+      </c>
+      <c r="BF38">
+        <v>2.6143628429398661E-2</v>
+      </c>
+      <c r="BG38">
+        <v>0.90941791130086391</v>
+      </c>
+      <c r="BH38">
+        <v>0.21707899283722051</v>
+      </c>
+      <c r="BI38">
+        <v>0.24786765398682961</v>
+      </c>
+      <c r="BJ38">
+        <v>3.5663918757243618E-2</v>
+      </c>
+      <c r="BK38">
+        <v>0.85682064675510383</v>
+      </c>
+      <c r="BL38">
+        <v>3.5663918757243618E-2</v>
+      </c>
+      <c r="BM38">
+        <v>3.5663918757243618E-2</v>
+      </c>
+      <c r="BN38">
+        <v>0.85682064675510383</v>
+      </c>
+      <c r="BO38">
+        <v>0.15977095995904991</v>
+      </c>
+      <c r="BP38">
+        <v>0.35857013162338802</v>
+      </c>
+      <c r="BQ38">
+        <v>45.004347765404759</v>
+      </c>
+      <c r="BR38">
+        <v>0.87190969290955456</v>
+      </c>
+      <c r="BS38">
+        <v>45.004347765404759</v>
+      </c>
+      <c r="BT38">
+        <v>45.004347765404759</v>
+      </c>
+      <c r="BU38">
+        <v>0.87190969290955456</v>
+      </c>
+      <c r="BV38">
+        <v>322.20161481202211</v>
+      </c>
+      <c r="BW38">
+        <v>8.2957406661170907E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46082.594247685192</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39">
+        <v>16590</v>
+      </c>
+      <c r="G39">
+        <v>4.5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s">
+        <v>79</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
+      </c>
+      <c r="L39" t="s">
+        <v>80</v>
+      </c>
+      <c r="M39" t="s">
+        <v>81</v>
+      </c>
+      <c r="N39" t="s">
+        <v>82</v>
+      </c>
+      <c r="O39" t="s">
+        <v>82</v>
+      </c>
+      <c r="P39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>84</v>
+      </c>
+      <c r="R39">
+        <v>3</v>
+      </c>
+      <c r="S39" t="s">
+        <v>85</v>
+      </c>
+      <c r="T39" t="s">
+        <v>86</v>
+      </c>
+      <c r="U39" t="s">
+        <v>87</v>
+      </c>
+      <c r="V39" t="s">
+        <v>88</v>
+      </c>
+      <c r="W39" t="s">
+        <v>89</v>
+      </c>
+      <c r="X39" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z39">
+        <v>4000</v>
+      </c>
+      <c r="AA39">
+        <v>4000</v>
+      </c>
+      <c r="AC39">
+        <v>512</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE39">
+        <v>0.15</v>
+      </c>
+      <c r="AF39">
+        <v>180</v>
+      </c>
+      <c r="AG39">
+        <v>60</v>
+      </c>
+      <c r="AH39">
+        <v>120</v>
+      </c>
+      <c r="AI39">
+        <v>8.644082322644582E-2</v>
+      </c>
+      <c r="AJ39">
+        <v>9.1869195750712009</v>
+      </c>
+      <c r="AK39">
+        <v>0.81424238599217835</v>
+      </c>
+      <c r="AL39">
+        <v>-0.4376571909467491</v>
+      </c>
+      <c r="AM39">
+        <v>12.705586239378309</v>
+      </c>
+      <c r="AN39">
+        <v>0.8194384355382428</v>
+      </c>
+      <c r="AO39">
+        <v>12.705586239378309</v>
+      </c>
+      <c r="AP39">
+        <v>12.705586239378309</v>
+      </c>
+      <c r="AQ39">
+        <v>0.8194384355382428</v>
+      </c>
+      <c r="AR39">
+        <v>110.37526131671351</v>
+      </c>
+      <c r="AS39">
+        <v>-0.34391961643249608</v>
+      </c>
+      <c r="AT39">
+        <v>0.8</v>
+      </c>
+      <c r="AU39" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV39">
+        <v>4.4795238792550887E-2</v>
+      </c>
+      <c r="AW39">
+        <v>0.67472864797972332</v>
+      </c>
+      <c r="AX39">
+        <v>4.4795238792550887E-2</v>
+      </c>
+      <c r="AY39">
+        <v>4.4795238792550887E-2</v>
+      </c>
+      <c r="AZ39">
+        <v>0.67472864797972332</v>
+      </c>
+      <c r="BA39">
+        <v>0.25848561526706332</v>
+      </c>
+      <c r="BB39">
+        <v>-0.87693977802150402</v>
+      </c>
+      <c r="BC39">
+        <v>2.9750587395985351E-2</v>
+      </c>
+      <c r="BD39">
+        <v>0.89692056886319005</v>
+      </c>
+      <c r="BE39">
+        <v>2.9750587395985351E-2</v>
+      </c>
+      <c r="BF39">
+        <v>2.9750587395985351E-2</v>
+      </c>
+      <c r="BG39">
+        <v>0.89692056886319005</v>
+      </c>
+      <c r="BH39">
+        <v>0.30557079131078307</v>
+      </c>
+      <c r="BI39">
+        <v>-5.8737527467805251E-2</v>
+      </c>
+      <c r="BJ39">
+        <v>3.7254323423080327E-2</v>
+      </c>
+      <c r="BK39">
+        <v>0.85043567506979478</v>
+      </c>
+      <c r="BL39">
+        <v>3.7254323423080327E-2</v>
+      </c>
+      <c r="BM39">
+        <v>3.7254323423080327E-2</v>
+      </c>
+      <c r="BN39">
+        <v>0.85043567506979478</v>
+      </c>
+      <c r="BO39">
+        <v>0.29538004849098981</v>
+      </c>
+      <c r="BP39">
+        <v>-0.18585746541933429</v>
+      </c>
+      <c r="BQ39">
+        <v>50.710544807901407</v>
+      </c>
+      <c r="BR39">
+        <v>0.85566885024026373</v>
+      </c>
+      <c r="BS39">
+        <v>50.710544807901407</v>
+      </c>
+      <c r="BT39">
+        <v>50.710544807901407</v>
+      </c>
+      <c r="BU39">
+        <v>0.85566885024026373</v>
+      </c>
+      <c r="BV39">
+        <v>440.64160881178668</v>
+      </c>
+      <c r="BW39">
+        <v>-0.25414369482134958</v>
+      </c>
+    </row>
+    <row r="40" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46082.91741898148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40">
+        <v>16590</v>
+      </c>
+      <c r="G40">
+        <v>4.5</v>
+      </c>
+      <c r="H40" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s">
+        <v>79</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
+      </c>
+      <c r="L40" t="s">
+        <v>80</v>
+      </c>
+      <c r="M40" t="s">
+        <v>81</v>
+      </c>
+      <c r="N40" t="s">
+        <v>82</v>
+      </c>
+      <c r="O40" t="s">
+        <v>82</v>
+      </c>
+      <c r="P40" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>84</v>
+      </c>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="S40" t="s">
+        <v>85</v>
+      </c>
+      <c r="T40" t="s">
+        <v>86</v>
+      </c>
+      <c r="U40" t="s">
+        <v>87</v>
+      </c>
+      <c r="V40" t="s">
+        <v>88</v>
+      </c>
+      <c r="W40" t="s">
+        <v>89</v>
+      </c>
+      <c r="X40" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z40">
+        <v>4000</v>
+      </c>
+      <c r="AA40">
+        <v>4000</v>
+      </c>
+      <c r="AC40">
+        <v>512</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE40">
+        <v>0.15</v>
+      </c>
+      <c r="AF40">
+        <v>180</v>
+      </c>
+      <c r="AG40">
+        <v>60</v>
+      </c>
+      <c r="AH40">
+        <v>120</v>
+      </c>
+      <c r="AI40">
+        <v>7.9983415010330086E-2</v>
+      </c>
+      <c r="AJ40">
+        <v>12.272633372581399</v>
+      </c>
+      <c r="AK40">
+        <v>0.8348849815197108</v>
+      </c>
+      <c r="AL40">
+        <v>-0.92529463933909406</v>
+      </c>
+      <c r="AM40">
+        <v>23.957640498508209</v>
+      </c>
+      <c r="AN40">
+        <v>0.79088617530242744</v>
+      </c>
+      <c r="AO40">
+        <v>23.957640498508209</v>
+      </c>
+      <c r="AP40">
+        <v>23.957640498508209</v>
+      </c>
+      <c r="AQ40">
+        <v>0.79088617530242744</v>
+      </c>
+      <c r="AR40">
+        <v>169.06649342462879</v>
+      </c>
+      <c r="AS40">
+        <v>-0.75504858565799149</v>
+      </c>
+      <c r="AT40">
+        <v>0.8</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV40">
+        <v>3.5541332828741307E-2</v>
+      </c>
+      <c r="AW40">
+        <v>0.74192397019368572</v>
+      </c>
+      <c r="AX40">
+        <v>3.5541332828741307E-2</v>
+      </c>
+      <c r="AY40">
+        <v>3.5541332828741307E-2</v>
+      </c>
+      <c r="AZ40">
+        <v>0.74192397019368572</v>
+      </c>
+      <c r="BA40">
+        <v>0.53223992353191174</v>
+      </c>
+      <c r="BB40">
+        <v>-2.86475000899387</v>
+      </c>
+      <c r="BC40">
+        <v>3.3017654948118882E-2</v>
+      </c>
+      <c r="BD40">
+        <v>0.88560087758190476</v>
+      </c>
+      <c r="BE40">
+        <v>3.3017654948118882E-2</v>
+      </c>
+      <c r="BF40">
+        <v>3.3017654948118882E-2</v>
+      </c>
+      <c r="BG40">
+        <v>0.88560087758190476</v>
+      </c>
+      <c r="BH40">
+        <v>0.17885269191039929</v>
+      </c>
+      <c r="BI40">
+        <v>0.38031362224804671</v>
+      </c>
+      <c r="BJ40">
+        <v>4.771494460530553E-2</v>
+      </c>
+      <c r="BK40">
+        <v>0.80843958973756636</v>
+      </c>
+      <c r="BL40">
+        <v>4.771494460530553E-2</v>
+      </c>
+      <c r="BM40">
+        <v>4.771494460530553E-2</v>
+      </c>
+      <c r="BN40">
+        <v>0.80843958973756636</v>
+      </c>
+      <c r="BO40">
+        <v>0.15280022543805241</v>
+      </c>
+      <c r="BP40">
+        <v>0.38655542586858582</v>
+      </c>
+      <c r="BQ40">
+        <v>95.714288061650677</v>
+      </c>
+      <c r="BR40">
+        <v>0.72758026369655293</v>
+      </c>
+      <c r="BS40">
+        <v>95.714288061650677</v>
+      </c>
+      <c r="BT40">
+        <v>95.714288061650677</v>
+      </c>
+      <c r="BU40">
+        <v>0.72758026369655293</v>
+      </c>
+      <c r="BV40">
+        <v>675.40208085763709</v>
+      </c>
+      <c r="BW40">
+        <v>-0.92231338175471733</v>
       </c>
     </row>
   </sheetData>
@@ -12642,7 +13563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AEA6F4-3101-46CE-BC02-B01BACDA33CE}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -13006,37 +13927,37 @@
         <v>512</v>
       </c>
       <c r="B10" s="10">
-        <v>0.76544513784457791</v>
+        <v>0.7740264568826577</v>
       </c>
       <c r="C10" s="10">
-        <v>-6.750701064517152E-2</v>
+        <v>-0.1041542080208263</v>
       </c>
       <c r="D10" s="10">
-        <v>0.61068073176673121</v>
+        <v>0.62516694095831682</v>
       </c>
       <c r="E10" s="10">
-        <v>0.85515051740520642</v>
+        <v>0.86042084263563723</v>
       </c>
       <c r="F10" s="10">
-        <v>0.74718107984177617</v>
+        <v>0.75860410784332366</v>
       </c>
       <c r="G10" s="10">
-        <v>0.82494377809828046</v>
+        <v>0.82412408945459414</v>
       </c>
       <c r="H10" s="10">
-        <v>-0.73470004635690345</v>
+        <v>-0.77627074293922116</v>
       </c>
       <c r="I10" s="10">
-        <v>0.29536398436514538</v>
+        <v>0.28217030918479685</v>
       </c>
       <c r="J10" s="10">
-        <v>0.31072901761277716</v>
+        <v>0.29519072758087334</v>
       </c>
       <c r="K10" s="10">
-        <v>-0.16246038474684268</v>
+        <v>-0.18771532289994133</v>
       </c>
       <c r="L10" s="10">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -14032,37 +14953,37 @@
         <v>143</v>
       </c>
       <c r="B37" s="10">
-        <v>0.85581484240928529</v>
+        <v>0.83952547821423384</v>
       </c>
       <c r="C37" s="10">
-        <v>0.26004526776887971</v>
+        <v>-0.20550212529558737</v>
       </c>
       <c r="D37" s="10">
-        <v>0.77593170988192284</v>
+        <v>0.73891073144504271</v>
       </c>
       <c r="E37" s="10">
-        <v>0.90583772727581424</v>
+        <v>0.89944427125544324</v>
       </c>
       <c r="F37" s="10">
-        <v>0.88223633777583421</v>
+        <v>0.84948306233457482</v>
       </c>
       <c r="G37" s="10">
-        <v>0.8437665141106383</v>
+        <v>0.82473133023925227</v>
       </c>
       <c r="H37" s="10">
-        <v>-0.85059955550855237</v>
+        <v>-1.013099103138722</v>
       </c>
       <c r="I37" s="10">
-        <v>0.62844746371773885</v>
+        <v>0.2994728031212025</v>
       </c>
       <c r="J37" s="10">
-        <v>0.64177689295394713</v>
+        <v>0.30026124625664663</v>
       </c>
       <c r="K37" s="10">
-        <v>-7.6907798932511984E-2</v>
+        <v>-0.292601867211852</v>
       </c>
       <c r="L37" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -14070,37 +14991,37 @@
         <v>0.15</v>
       </c>
       <c r="B38" s="10">
-        <v>0.85581484240928529</v>
+        <v>0.83952547821423384</v>
       </c>
       <c r="C38" s="10">
-        <v>0.26004526776887971</v>
+        <v>-0.20550212529558737</v>
       </c>
       <c r="D38" s="10">
-        <v>0.77593170988192284</v>
+        <v>0.73891073144504271</v>
       </c>
       <c r="E38" s="10">
-        <v>0.90583772727581424</v>
+        <v>0.89944427125544324</v>
       </c>
       <c r="F38" s="10">
-        <v>0.88223633777583421</v>
+        <v>0.84948306233457482</v>
       </c>
       <c r="G38" s="10">
-        <v>0.8437665141106383</v>
+        <v>0.82473133023925227</v>
       </c>
       <c r="H38" s="10">
-        <v>-0.85059955550855237</v>
+        <v>-1.013099103138722</v>
       </c>
       <c r="I38" s="10">
-        <v>0.62844746371773885</v>
+        <v>0.2994728031212025</v>
       </c>
       <c r="J38" s="10">
-        <v>0.64177689295394713</v>
+        <v>0.30026124625664663</v>
       </c>
       <c r="K38" s="10">
-        <v>-7.6907798932511984E-2</v>
+        <v>-0.292601867211852</v>
       </c>
       <c r="L38" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -14142,266 +15063,266 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <v>1024</v>
+      <c r="A40" s="7">
+        <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>0.54507496754304918</v>
+        <v>0.85315970293576116</v>
       </c>
       <c r="C40" s="10">
-        <v>-0.14494785652419145</v>
+        <v>0.28089806133461392</v>
       </c>
       <c r="D40" s="10">
-        <v>0.35990404861370839</v>
+        <v>0.76305859772483908</v>
       </c>
       <c r="E40" s="10">
-        <v>0.71059100545035214</v>
+        <v>0.90941791130086391</v>
       </c>
       <c r="F40" s="10">
-        <v>0.47754947446814872</v>
+        <v>0.85682064675510383</v>
       </c>
       <c r="G40" s="10">
-        <v>0.70452761123883101</v>
+        <v>0.87190969290955456</v>
       </c>
       <c r="H40" s="10">
-        <v>-0.38864148321049863</v>
+        <v>0.53989292996903793</v>
       </c>
       <c r="I40" s="10">
-        <v>8.9076829614158082E-2</v>
+        <v>0.24786765398682961</v>
       </c>
       <c r="J40" s="10">
-        <v>0.10018360224529324</v>
+        <v>0.35857013162338802</v>
       </c>
       <c r="K40" s="10">
-        <v>-0.15181867253603026</v>
+        <v>8.2957406661170907E-2</v>
       </c>
       <c r="L40" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>91</v>
+      <c r="A41" s="7">
+        <v>3</v>
       </c>
       <c r="B41" s="10">
-        <v>0.74924138854953315</v>
+        <v>0.81424238599217835</v>
       </c>
       <c r="C41" s="10">
-        <v>-8.849625864658725E-2</v>
+        <v>-0.4376571909467491</v>
       </c>
       <c r="D41" s="10">
-        <v>0.58934326207549126</v>
+        <v>0.67472864797972332</v>
       </c>
       <c r="E41" s="10">
-        <v>0.84860775551704504</v>
+        <v>0.89692056886319005</v>
       </c>
       <c r="F41" s="10">
-        <v>0.72233815881884555</v>
+        <v>0.85043567506979478</v>
       </c>
       <c r="G41" s="10">
-        <v>0.82639235656347443</v>
+        <v>0.85566885024026373</v>
       </c>
       <c r="H41" s="10">
-        <v>-0.51366844206920037</v>
+        <v>-0.87693977802150402</v>
       </c>
       <c r="I41" s="10">
-        <v>0.26025272902454277</v>
+        <v>-5.8737527467805251E-2</v>
       </c>
       <c r="J41" s="10">
-        <v>0.26349721687193661</v>
+        <v>-0.18585746541933429</v>
       </c>
       <c r="K41" s="10">
-        <v>-9.4443145194353414E-2</v>
+        <v>-0.25414369482134958</v>
       </c>
       <c r="L41" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
-        <v>0.1</v>
+      <c r="A42" s="7">
+        <v>4</v>
       </c>
       <c r="B42" s="10">
-        <v>0.74924138854953315</v>
+        <v>0.8348849815197108</v>
       </c>
       <c r="C42" s="10">
-        <v>-8.849625864658725E-2</v>
+        <v>-0.92529463933909406</v>
       </c>
       <c r="D42" s="10">
-        <v>0.58934326207549126</v>
+        <v>0.74192397019368572</v>
       </c>
       <c r="E42" s="10">
-        <v>0.84860775551704504</v>
+        <v>0.88560087758190476</v>
       </c>
       <c r="F42" s="10">
-        <v>0.72233815881884555</v>
+        <v>0.80843958973756636</v>
       </c>
       <c r="G42" s="10">
-        <v>0.82639235656347443</v>
+        <v>0.72758026369655293</v>
       </c>
       <c r="H42" s="10">
-        <v>-0.51366844206920037</v>
+        <v>-2.86475000899387</v>
       </c>
       <c r="I42" s="10">
-        <v>0.26025272902454277</v>
+        <v>0.38031362224804671</v>
       </c>
       <c r="J42" s="10">
-        <v>0.26349721687193661</v>
+        <v>0.38655542586858582</v>
       </c>
       <c r="K42" s="10">
-        <v>-9.4443145194353414E-2</v>
+        <v>-0.92231338175471733</v>
       </c>
       <c r="L42" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
-        <v>1</v>
+      <c r="A43" s="3">
+        <v>1024</v>
       </c>
       <c r="B43" s="10">
-        <v>0.7687160329509809</v>
+        <v>0.54507496754304918</v>
       </c>
       <c r="C43" s="10">
-        <v>-0.1018973670859001</v>
+        <v>-0.14494785652419145</v>
       </c>
       <c r="D43" s="10">
-        <v>0.69700802149058638</v>
+        <v>0.35990404861370839</v>
       </c>
       <c r="E43" s="10">
-        <v>0.83890398810674194</v>
+        <v>0.71059100545035214</v>
       </c>
       <c r="F43" s="10">
-        <v>0.67893628865697231</v>
+        <v>0.47754947446814872</v>
       </c>
       <c r="G43" s="10">
-        <v>0.85066045471301566</v>
+        <v>0.70452761123883101</v>
       </c>
       <c r="H43" s="10">
-        <v>-0.67261580953703159</v>
+        <v>-0.38864148321049863</v>
       </c>
       <c r="I43" s="10">
-        <v>0.30848244788702678</v>
+        <v>8.9076829614158082E-2</v>
       </c>
       <c r="J43" s="10">
-        <v>0.31495528196096989</v>
+        <v>0.10018360224529324</v>
       </c>
       <c r="K43" s="10">
-        <v>-6.2549910870268954E-2</v>
+        <v>-0.15181867253603026</v>
       </c>
       <c r="L43" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
-        <v>2</v>
+      <c r="A44" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B44" s="10">
-        <v>0.79442331710326963</v>
+        <v>0.74924138854953315</v>
       </c>
       <c r="C44" s="10">
-        <v>0.18890428306448309</v>
+        <v>-8.849625864658725E-2</v>
       </c>
       <c r="D44" s="10">
-        <v>0.69461192756619639</v>
+        <v>0.58934326207549126</v>
       </c>
       <c r="E44" s="10">
-        <v>0.87843299561426591</v>
+        <v>0.84860775551704504</v>
       </c>
       <c r="F44" s="10">
-        <v>0.76870774427119959</v>
+        <v>0.72233815881884555</v>
       </c>
       <c r="G44" s="10">
-        <v>0.8657777210859523</v>
+        <v>0.82639235656347443</v>
       </c>
       <c r="H44" s="10">
-        <v>0.2442860439736072</v>
+        <v>-0.51366844206920037</v>
       </c>
       <c r="I44" s="10">
-        <v>0.27498782728922072</v>
+        <v>0.26025272902454277</v>
       </c>
       <c r="J44" s="10">
-        <v>0.31344779846252901</v>
+        <v>0.26349721687193661</v>
       </c>
       <c r="K44" s="10">
-        <v>0.20383816913817321</v>
+        <v>-9.4443145194353414E-2</v>
       </c>
       <c r="L44" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
-        <v>3</v>
+      <c r="A45" s="5">
+        <v>0.1</v>
       </c>
       <c r="B45" s="10">
-        <v>0.76288008972886723</v>
+        <v>0.74924138854953315</v>
       </c>
       <c r="C45" s="10">
-        <v>-0.2346253602248935</v>
+        <v>-8.849625864658725E-2</v>
       </c>
       <c r="D45" s="10">
-        <v>0.56217227264353165</v>
+        <v>0.58934326207549126</v>
       </c>
       <c r="E45" s="10">
-        <v>0.8860302856604424</v>
+        <v>0.84860775551704504</v>
       </c>
       <c r="F45" s="10">
-        <v>0.8193006606391926</v>
+        <v>0.72233815881884555</v>
       </c>
       <c r="G45" s="10">
-        <v>0.82516830197440383</v>
+        <v>0.82639235656347443</v>
       </c>
       <c r="H45" s="10">
-        <v>-0.68138424664239317</v>
+        <v>-0.51366844206920037</v>
       </c>
       <c r="I45" s="10">
-        <v>0.26100581310338711</v>
+        <v>0.26025272902454277</v>
       </c>
       <c r="J45" s="10">
-        <v>0.19683381507042591</v>
+        <v>0.26349721687193661</v>
       </c>
       <c r="K45" s="10">
-        <v>-0.32598079507706462</v>
+        <v>-9.4443145194353414E-2</v>
       </c>
       <c r="L45" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B46" s="10">
-        <v>0.76118150293457421</v>
+        <v>0.7687160329509809</v>
       </c>
       <c r="C46" s="10">
-        <v>-0.18115312472614889</v>
+        <v>-0.1018973670859001</v>
       </c>
       <c r="D46" s="10">
-        <v>0.62772005551197863</v>
+        <v>0.69700802149058638</v>
       </c>
       <c r="E46" s="10">
-        <v>0.83191185108329491</v>
+        <v>0.83890398810674194</v>
       </c>
       <c r="F46" s="10">
-        <v>0.6996564818337313</v>
+        <v>0.67893628865697231</v>
       </c>
       <c r="G46" s="10">
-        <v>0.77588049834428796</v>
+        <v>0.85066045471301566</v>
       </c>
       <c r="H46" s="10">
-        <v>-1.1287324429254719</v>
+        <v>-0.67261580953703159</v>
       </c>
       <c r="I46" s="10">
-        <v>0.52018665256350383</v>
+        <v>0.30848244788702678</v>
       </c>
       <c r="J46" s="10">
-        <v>0.53041945251480216</v>
+        <v>0.31495528196096989</v>
       </c>
       <c r="K46" s="10">
-        <v>-7.7928630103461183E-2</v>
+        <v>-6.2549910870268954E-2</v>
       </c>
       <c r="L46" s="10">
         <v>1</v>
@@ -14409,265 +15330,265 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B47" s="10">
-        <v>0.65900600002997334</v>
+        <v>0.79442331710326963</v>
       </c>
       <c r="C47" s="10">
-        <v>-0.1137097242604768</v>
+        <v>0.18890428306448309</v>
       </c>
       <c r="D47" s="10">
-        <v>0.36520403316516331</v>
+        <v>0.69461192756619639</v>
       </c>
       <c r="E47" s="10">
-        <v>0.80775965712048059</v>
+        <v>0.87843299561426591</v>
       </c>
       <c r="F47" s="10">
-        <v>0.64508961869313208</v>
+        <v>0.76870774427119959</v>
       </c>
       <c r="G47" s="10">
-        <v>0.81447480669971251</v>
+        <v>0.8657777210859523</v>
       </c>
       <c r="H47" s="10">
-        <v>-0.32989575521471209</v>
+        <v>0.2442860439736072</v>
       </c>
       <c r="I47" s="10">
-        <v>-6.3399095720424459E-2</v>
+        <v>0.27498782728922072</v>
       </c>
       <c r="J47" s="10">
-        <v>-3.8170263649043967E-2</v>
+        <v>0.31344779846252901</v>
       </c>
       <c r="K47" s="10">
-        <v>-0.20959455905914551</v>
+        <v>0.20383816913817321</v>
       </c>
       <c r="L47" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>133</v>
+      <c r="A48" s="7">
+        <v>3</v>
       </c>
       <c r="B48" s="10">
-        <v>0.34090854653656527</v>
+        <v>0.76288008972886723</v>
       </c>
       <c r="C48" s="10">
-        <v>-0.20139945440179563</v>
+        <v>-0.2346253602248935</v>
       </c>
       <c r="D48" s="10">
-        <v>0.13046483515192558</v>
+        <v>0.56217227264353165</v>
       </c>
       <c r="E48" s="10">
-        <v>0.57257425538365925</v>
+        <v>0.8860302856604424</v>
       </c>
       <c r="F48" s="10">
-        <v>0.23276079011745207</v>
+        <v>0.8193006606391926</v>
       </c>
       <c r="G48" s="10">
-        <v>0.58266286591418781</v>
+        <v>0.82516830197440383</v>
       </c>
       <c r="H48" s="10">
-        <v>-0.26361452435179689</v>
+        <v>-0.68138424664239317</v>
       </c>
       <c r="I48" s="10">
-        <v>-8.2099069796226637E-2</v>
+        <v>0.26100581310338711</v>
       </c>
       <c r="J48" s="10">
-        <v>-6.3130012381350117E-2</v>
+        <v>0.19683381507042591</v>
       </c>
       <c r="K48" s="10">
-        <v>-0.2091941998777071</v>
+        <v>-0.32598079507706462</v>
       </c>
       <c r="L48" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
-        <v>0.05</v>
+      <c r="A49" s="7">
+        <v>4</v>
       </c>
       <c r="B49" s="10">
-        <v>0.34090854653656527</v>
+        <v>0.76118150293457421</v>
       </c>
       <c r="C49" s="10">
-        <v>-0.20139945440179563</v>
+        <v>-0.18115312472614889</v>
       </c>
       <c r="D49" s="10">
-        <v>0.13046483515192558</v>
+        <v>0.62772005551197863</v>
       </c>
       <c r="E49" s="10">
-        <v>0.57257425538365925</v>
+        <v>0.83191185108329491</v>
       </c>
       <c r="F49" s="10">
-        <v>0.23276079011745207</v>
+        <v>0.6996564818337313</v>
       </c>
       <c r="G49" s="10">
-        <v>0.58266286591418781</v>
+        <v>0.77588049834428796</v>
       </c>
       <c r="H49" s="10">
-        <v>-0.26361452435179689</v>
+        <v>-1.1287324429254719</v>
       </c>
       <c r="I49" s="10">
-        <v>-8.2099069796226637E-2</v>
+        <v>0.52018665256350383</v>
       </c>
       <c r="J49" s="10">
-        <v>-6.3130012381350117E-2</v>
+        <v>0.53041945251480216</v>
       </c>
       <c r="K49" s="10">
-        <v>-0.2091941998777071</v>
+        <v>-7.7928630103461183E-2</v>
       </c>
       <c r="L49" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B50" s="10">
-        <v>0.36236966024911332</v>
+        <v>0.65900600002997334</v>
       </c>
       <c r="C50" s="10">
-        <v>-0.2203559043159494</v>
+        <v>-0.1137097242604768</v>
       </c>
       <c r="D50" s="10">
-        <v>0.21221737882565619</v>
+        <v>0.36520403316516331</v>
       </c>
       <c r="E50" s="10">
-        <v>0.5433972549649968</v>
+        <v>0.80775965712048059</v>
       </c>
       <c r="F50" s="10">
-        <v>0.1798672964141548</v>
+        <v>0.64508961869313208</v>
       </c>
       <c r="G50" s="10">
-        <v>0.69610748218738094</v>
+        <v>0.81447480669971251</v>
       </c>
       <c r="H50" s="10">
-        <v>-0.39082763040243362</v>
+        <v>-0.32989575521471209</v>
       </c>
       <c r="I50" s="10">
-        <v>-5.9943945711704361E-2</v>
+        <v>-6.3399095720424459E-2</v>
       </c>
       <c r="J50" s="10">
-        <v>-9.2893487104375616E-2</v>
+        <v>-3.8170263649043967E-2</v>
       </c>
       <c r="K50" s="10">
-        <v>-0.22449729398133139</v>
+        <v>-0.20959455905914551</v>
       </c>
       <c r="L50" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
-        <v>2</v>
+      <c r="A51" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="B51" s="10">
-        <v>0.36730705242407818</v>
+        <v>0.34090854653656527</v>
       </c>
       <c r="C51" s="10">
-        <v>-0.18502663943294051</v>
+        <v>-0.20139945440179563</v>
       </c>
       <c r="D51" s="10">
-        <v>0.19814482058725269</v>
+        <v>0.13046483515192558</v>
       </c>
       <c r="E51" s="10">
-        <v>0.63902400539696647</v>
+        <v>0.57257425538365925</v>
       </c>
       <c r="F51" s="10">
-        <v>0.18398279220589681</v>
+        <v>0.23276079011745207</v>
       </c>
       <c r="G51" s="10">
-        <v>0.63182416593721968</v>
+        <v>0.58266286591418781</v>
       </c>
       <c r="H51" s="10">
-        <v>-0.21149501268980539</v>
+        <v>-0.26361452435179689</v>
       </c>
       <c r="I51" s="10">
-        <v>-0.1158541526438668</v>
+        <v>-8.2099069796226637E-2</v>
       </c>
       <c r="J51" s="10">
-        <v>-0.142929672603894</v>
+        <v>-6.3130012381350117E-2</v>
       </c>
       <c r="K51" s="10">
-        <v>-5.3946416691347247E-2</v>
+        <v>-0.2091941998777071</v>
       </c>
       <c r="L51" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
-        <v>3</v>
+      <c r="A52" s="5">
+        <v>0.05</v>
       </c>
       <c r="B52" s="10">
-        <v>0.30908052594271451</v>
+        <v>0.34090854653656527</v>
       </c>
       <c r="C52" s="10">
-        <v>-0.25846877494804849</v>
+        <v>-0.20139945440179563</v>
       </c>
       <c r="D52" s="10">
-        <v>0.13574346461914649</v>
+        <v>0.13046483515192558</v>
       </c>
       <c r="E52" s="10">
-        <v>0.60187189283430609</v>
+        <v>0.57257425538365925</v>
       </c>
       <c r="F52" s="10">
-        <v>0.21583975245046169</v>
+        <v>0.23276079011745207</v>
       </c>
       <c r="G52" s="10">
-        <v>0.52511659288826185</v>
+        <v>0.58266286591418781</v>
       </c>
       <c r="H52" s="10">
-        <v>-0.33036074734245952</v>
+        <v>-0.26361452435179689</v>
       </c>
       <c r="I52" s="10">
-        <v>-3.5325060111648147E-2</v>
+        <v>-8.2099069796226637E-2</v>
       </c>
       <c r="J52" s="10">
-        <v>-1.97031750299963E-2</v>
+        <v>-6.3130012381350117E-2</v>
       </c>
       <c r="K52" s="10">
-        <v>-0.37479497702385262</v>
+        <v>-0.2091941998777071</v>
       </c>
       <c r="L52" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B53" s="10">
-        <v>0.36397912468366639</v>
+        <v>0.36236966024911332</v>
       </c>
       <c r="C53" s="10">
-        <v>-0.1168826118850578</v>
+        <v>-0.2203559043159494</v>
       </c>
       <c r="D53" s="10">
-        <v>0.19785684542918791</v>
+        <v>0.21221737882565619</v>
       </c>
       <c r="E53" s="10">
-        <v>0.53991517975978209</v>
+        <v>0.5433972549649968</v>
       </c>
       <c r="F53" s="10">
-        <v>0.28724917217649659</v>
+        <v>0.1798672964141548</v>
       </c>
       <c r="G53" s="10">
-        <v>0.53079985956210807</v>
+        <v>0.69610748218738094</v>
       </c>
       <c r="H53" s="10">
-        <v>-0.24212628071734391</v>
+        <v>-0.39082763040243362</v>
       </c>
       <c r="I53" s="10">
-        <v>-6.3695226693954998E-2</v>
+        <v>-5.9943945711704361E-2</v>
       </c>
       <c r="J53" s="10">
-        <v>-1.614183840791128E-2</v>
+        <v>-9.2893487104375616E-2</v>
       </c>
       <c r="K53" s="10">
-        <v>-4.6905790899782973E-2</v>
+        <v>-0.22449729398133139</v>
       </c>
       <c r="L53" s="10">
         <v>1</v>
@@ -14675,78 +15596,192 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B54" s="10">
-        <v>0.30180636938325411</v>
+        <v>0.36730705242407818</v>
       </c>
       <c r="C54" s="10">
-        <v>-0.22626334142698201</v>
+        <v>-0.18502663943294051</v>
       </c>
       <c r="D54" s="10">
-        <v>-9.1638333701615338E-2</v>
+        <v>0.19814482058725269</v>
       </c>
       <c r="E54" s="10">
-        <v>0.53866294396224468</v>
+        <v>0.63902400539696647</v>
       </c>
       <c r="F54" s="10">
-        <v>0.29686493734025049</v>
+        <v>0.18398279220589681</v>
       </c>
       <c r="G54" s="10">
-        <v>0.5294662289959684</v>
+        <v>0.63182416593721968</v>
       </c>
       <c r="H54" s="10">
-        <v>-0.14326295060694211</v>
+        <v>-0.21149501268980539</v>
       </c>
       <c r="I54" s="10">
-        <v>-0.13567696381995889</v>
+        <v>-0.1158541526438668</v>
       </c>
       <c r="J54" s="10">
-        <v>-4.3981888760573407E-2</v>
+        <v>-0.142929672603894</v>
       </c>
       <c r="K54" s="10">
-        <v>-0.34582652079222131</v>
+        <v>-5.3946416691347247E-2</v>
       </c>
       <c r="L54" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="7">
+        <v>3</v>
+      </c>
+      <c r="B55" s="10">
+        <v>0.30908052594271451</v>
+      </c>
+      <c r="C55" s="10">
+        <v>-0.25846877494804849</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0.13574346461914649</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.60187189283430609</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0.21583975245046169</v>
+      </c>
+      <c r="G55" s="10">
+        <v>0.52511659288826185</v>
+      </c>
+      <c r="H55" s="10">
+        <v>-0.33036074734245952</v>
+      </c>
+      <c r="I55" s="10">
+        <v>-3.5325060111648147E-2</v>
+      </c>
+      <c r="J55" s="10">
+        <v>-1.97031750299963E-2</v>
+      </c>
+      <c r="K55" s="10">
+        <v>-0.37479497702385262</v>
+      </c>
+      <c r="L55" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="7">
+        <v>4</v>
+      </c>
+      <c r="B56" s="10">
+        <v>0.36397912468366639</v>
+      </c>
+      <c r="C56" s="10">
+        <v>-0.1168826118850578</v>
+      </c>
+      <c r="D56" s="10">
+        <v>0.19785684542918791</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.53991517975978209</v>
+      </c>
+      <c r="F56" s="10">
+        <v>0.28724917217649659</v>
+      </c>
+      <c r="G56" s="10">
+        <v>0.53079985956210807</v>
+      </c>
+      <c r="H56" s="10">
+        <v>-0.24212628071734391</v>
+      </c>
+      <c r="I56" s="10">
+        <v>-6.3695226693954998E-2</v>
+      </c>
+      <c r="J56" s="10">
+        <v>-1.614183840791128E-2</v>
+      </c>
+      <c r="K56" s="10">
+        <v>-4.6905790899782973E-2</v>
+      </c>
+      <c r="L56" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="7">
+        <v>5</v>
+      </c>
+      <c r="B57" s="10">
+        <v>0.30180636938325411</v>
+      </c>
+      <c r="C57" s="10">
+        <v>-0.22626334142698201</v>
+      </c>
+      <c r="D57" s="10">
+        <v>-9.1638333701615338E-2</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.53866294396224468</v>
+      </c>
+      <c r="F57" s="10">
+        <v>0.29686493734025049</v>
+      </c>
+      <c r="G57" s="10">
+        <v>0.5294662289959684</v>
+      </c>
+      <c r="H57" s="10">
+        <v>-0.14326295060694211</v>
+      </c>
+      <c r="I57" s="10">
+        <v>-0.13567696381995889</v>
+      </c>
+      <c r="J57" s="10">
+        <v>-4.3981888760573407E-2</v>
+      </c>
+      <c r="K57" s="10">
+        <v>-0.34582652079222131</v>
+      </c>
+      <c r="L57" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B55" s="10">
-        <v>0.70126304377085991</v>
-      </c>
-      <c r="C55" s="10">
-        <v>-8.545235600558887E-2</v>
-      </c>
-      <c r="D55" s="10">
-        <v>0.53630711459193803</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0.81359202822632382</v>
-      </c>
-      <c r="F55" s="10">
-        <v>0.66858835605528266</v>
-      </c>
-      <c r="G55" s="10">
-        <v>0.79149665776106404</v>
-      </c>
-      <c r="H55" s="10">
-        <v>-0.60402472728604295</v>
-      </c>
-      <c r="I55" s="10">
-        <v>0.2382201094764145</v>
-      </c>
-      <c r="J55" s="10">
-        <v>0.25051497607439394</v>
-      </c>
-      <c r="K55" s="10">
-        <v>-0.15328902372903477</v>
-      </c>
-      <c r="L55" s="10">
-        <v>36</v>
+      <c r="B58" s="10">
+        <v>0.71148093964611814</v>
+      </c>
+      <c r="C58" s="10">
+        <v>-0.1066240662859597</v>
+      </c>
+      <c r="D58" s="10">
+        <v>0.55094275233866719</v>
+      </c>
+      <c r="E58" s="10">
+        <v>0.82003211215111838</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0.68166350588596503</v>
+      </c>
+      <c r="G58" s="10">
+        <v>0.7935650893908891</v>
+      </c>
+      <c r="H58" s="10">
+        <v>-0.63965864203445855</v>
+      </c>
+      <c r="I58" s="10">
+        <v>0.23449660743379469</v>
+      </c>
+      <c r="J58" s="10">
+        <v>0.24558480078848269</v>
+      </c>
+      <c r="K58" s="10">
+        <v>-0.1695360134400038</v>
+      </c>
+      <c r="L58" s="10">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/Final_winner_optimization.xlsx
+++ b/logs/final_winner_optimization/Final_winner_optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/final_winner_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B45ABE83-0528-454B-B1FE-0988A4535BE6}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D32870F-A697-4718-B2CA-DB35766B3358}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="148">
   <si>
     <t>date</t>
   </si>
@@ -471,6 +471,9 @@
   <si>
     <t>03-01_22-01-05_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
   </si>
+  <si>
+    <t>03-02_05-07-38_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -614,13 +617,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46083.419104976849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="39" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46083.677971064812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-01T22:01:05"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-02T05:07:38"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -770,7 +773,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.31833894414921388" maxValue="0.85194307226105237"/>
     </cacheField>
     <cacheField name="global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="69.623397543544598" maxValue="169.06649342462879"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="57.717802551716687" maxValue="169.06649342462879"/>
     </cacheField>
     <cacheField name="global closed R2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.84376231738702545" maxValue="0.30732203056010721"/>
@@ -860,10 +863,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.52511659288826185" maxValue="0.87190969290955456"/>
     </cacheField>
     <cacheField name="Yaw Angle Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="278.00904088934652" maxValue="675.40208085763709"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="230.45239689593109" maxValue="675.40208085763709"/>
     </cacheField>
     <cacheField name="Yaw Angle Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.92231338175471733" maxValue="0.20873726229601061"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.92231338175471733" maxValue="0.34409185436922768"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -875,7 +878,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="39">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
   <r>
     <d v="2026-02-16T18:21:04"/>
     <s v="02-16_18-21-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
@@ -3879,12 +3882,89 @@
     <n v="675.40208085763709"/>
     <n v="-0.92231338175471733"/>
   </r>
+  <r>
+    <d v="2026-03-02T05:07:38"/>
+    <s v="03-02_05-07-38_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="9.0722454404960004E-2"/>
+    <n v="10.090909115303839"/>
+    <n v="0.81580094370282341"/>
+    <n v="9.150152026974967E-2"/>
+    <n v="13.086614090072629"/>
+    <n v="0.80743534177394172"/>
+    <n v="13.086614090072629"/>
+    <n v="13.086614090072629"/>
+    <n v="0.80743534177394172"/>
+    <n v="57.717802551716687"/>
+    <n v="0.25888273537445478"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="3.97363564214493E-2"/>
+    <n v="0.71146267491906379"/>
+    <n v="3.97363564214493E-2"/>
+    <n v="3.97363564214493E-2"/>
+    <n v="0.71146267491906379"/>
+    <n v="0.21008476557675701"/>
+    <n v="-0.52548702897813637"/>
+    <n v="3.7381591928115923E-2"/>
+    <n v="0.87048076800465024"/>
+    <n v="3.7381591928115923E-2"/>
+    <n v="3.7381591928115923E-2"/>
+    <n v="0.87048076800465024"/>
+    <n v="9.9846292153675117E-2"/>
+    <n v="0.6540539230593676"/>
+    <n v="5.0708515382616642E-2"/>
+    <n v="0.79642134993880132"/>
+    <n v="5.0708515382616642E-2"/>
+    <n v="5.0708515382616642E-2"/>
+    <n v="0.79642134993880132"/>
+    <n v="0.1088822532046668"/>
+    <n v="0.56287219304735481"/>
+    <n v="52.218629896557722"/>
+    <n v="0.85137657423325541"/>
+    <n v="52.218629896557722"/>
+    <n v="52.218629896557722"/>
+    <n v="0.85137657423325541"/>
+    <n v="230.45239689593109"/>
+    <n v="0.34409185436922768"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24326305-70A8-4C78-9FE9-6DC3DEA8AA33}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:L58" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A1:L59" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -4001,7 +4081,7 @@
     <field x="30"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="57">
+  <rowItems count="58">
     <i>
       <x/>
     </i>
@@ -4125,6 +4205,9 @@
     <i r="3">
       <x v="3"/>
     </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
@@ -4238,7 +4321,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW40" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW41" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <tableColumns count="75">
     <tableColumn id="1" xr3:uid="{E29847FD-796C-4D7F-957B-1B478BBCCC1D}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{AFC0F8DD-B9EA-4787-891C-59254C048BBB}" name="model_id"/>
@@ -4583,7 +4666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW40"/>
+  <dimension ref="A1:BW41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="42" max="42" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -13551,6 +13634,230 @@
       </c>
       <c r="BW40">
         <v>-0.92231338175471733</v>
+      </c>
+    </row>
+    <row r="41" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46083.213634259257</v>
+      </c>
+      <c r="B41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41">
+        <v>16590</v>
+      </c>
+      <c r="G41">
+        <v>4.5</v>
+      </c>
+      <c r="H41" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s">
+        <v>79</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41" t="s">
+        <v>80</v>
+      </c>
+      <c r="M41" t="s">
+        <v>81</v>
+      </c>
+      <c r="N41" t="s">
+        <v>82</v>
+      </c>
+      <c r="O41" t="s">
+        <v>82</v>
+      </c>
+      <c r="P41" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>84</v>
+      </c>
+      <c r="R41">
+        <v>3</v>
+      </c>
+      <c r="S41" t="s">
+        <v>85</v>
+      </c>
+      <c r="T41" t="s">
+        <v>86</v>
+      </c>
+      <c r="U41" t="s">
+        <v>87</v>
+      </c>
+      <c r="V41" t="s">
+        <v>88</v>
+      </c>
+      <c r="W41" t="s">
+        <v>89</v>
+      </c>
+      <c r="X41" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z41">
+        <v>4000</v>
+      </c>
+      <c r="AA41">
+        <v>4000</v>
+      </c>
+      <c r="AC41">
+        <v>512</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE41">
+        <v>0.15</v>
+      </c>
+      <c r="AF41">
+        <v>180</v>
+      </c>
+      <c r="AG41">
+        <v>60</v>
+      </c>
+      <c r="AH41">
+        <v>120</v>
+      </c>
+      <c r="AI41">
+        <v>9.0722454404960004E-2</v>
+      </c>
+      <c r="AJ41">
+        <v>10.090909115303839</v>
+      </c>
+      <c r="AK41">
+        <v>0.81580094370282341</v>
+      </c>
+      <c r="AL41">
+        <v>9.150152026974967E-2</v>
+      </c>
+      <c r="AM41">
+        <v>13.086614090072629</v>
+      </c>
+      <c r="AN41">
+        <v>0.80743534177394172</v>
+      </c>
+      <c r="AO41">
+        <v>13.086614090072629</v>
+      </c>
+      <c r="AP41">
+        <v>13.086614090072629</v>
+      </c>
+      <c r="AQ41">
+        <v>0.80743534177394172</v>
+      </c>
+      <c r="AR41">
+        <v>57.717802551716687</v>
+      </c>
+      <c r="AS41">
+        <v>0.25888273537445478</v>
+      </c>
+      <c r="AT41">
+        <v>0.8</v>
+      </c>
+      <c r="AU41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV41">
+        <v>3.97363564214493E-2</v>
+      </c>
+      <c r="AW41">
+        <v>0.71146267491906379</v>
+      </c>
+      <c r="AX41">
+        <v>3.97363564214493E-2</v>
+      </c>
+      <c r="AY41">
+        <v>3.97363564214493E-2</v>
+      </c>
+      <c r="AZ41">
+        <v>0.71146267491906379</v>
+      </c>
+      <c r="BA41">
+        <v>0.21008476557675701</v>
+      </c>
+      <c r="BB41">
+        <v>-0.52548702897813637</v>
+      </c>
+      <c r="BC41">
+        <v>3.7381591928115923E-2</v>
+      </c>
+      <c r="BD41">
+        <v>0.87048076800465024</v>
+      </c>
+      <c r="BE41">
+        <v>3.7381591928115923E-2</v>
+      </c>
+      <c r="BF41">
+        <v>3.7381591928115923E-2</v>
+      </c>
+      <c r="BG41">
+        <v>0.87048076800465024</v>
+      </c>
+      <c r="BH41">
+        <v>9.9846292153675117E-2</v>
+      </c>
+      <c r="BI41">
+        <v>0.6540539230593676</v>
+      </c>
+      <c r="BJ41">
+        <v>5.0708515382616642E-2</v>
+      </c>
+      <c r="BK41">
+        <v>0.79642134993880132</v>
+      </c>
+      <c r="BL41">
+        <v>5.0708515382616642E-2</v>
+      </c>
+      <c r="BM41">
+        <v>5.0708515382616642E-2</v>
+      </c>
+      <c r="BN41">
+        <v>0.79642134993880132</v>
+      </c>
+      <c r="BO41">
+        <v>0.1088822532046668</v>
+      </c>
+      <c r="BP41">
+        <v>0.56287219304735481</v>
+      </c>
+      <c r="BQ41">
+        <v>52.218629896557722</v>
+      </c>
+      <c r="BR41">
+        <v>0.85137657423325541</v>
+      </c>
+      <c r="BS41">
+        <v>52.218629896557722</v>
+      </c>
+      <c r="BT41">
+        <v>52.218629896557722</v>
+      </c>
+      <c r="BU41">
+        <v>0.85137657423325541</v>
+      </c>
+      <c r="BV41">
+        <v>230.45239689593109</v>
+      </c>
+      <c r="BW41">
+        <v>0.34409185436922768</v>
       </c>
     </row>
   </sheetData>
@@ -13563,7 +13870,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AEA6F4-3101-46CE-BC02-B01BACDA33CE}">
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -13927,37 +14234,37 @@
         <v>512</v>
       </c>
       <c r="B10" s="10">
-        <v>0.7740264568826577</v>
+        <v>0.77569743635546429</v>
       </c>
       <c r="C10" s="10">
-        <v>-0.1041542080208263</v>
+        <v>-9.6327978889203261E-2</v>
       </c>
       <c r="D10" s="10">
-        <v>0.62516694095831682</v>
+        <v>0.62861877031674662</v>
       </c>
       <c r="E10" s="10">
-        <v>0.86042084263563723</v>
+        <v>0.86082323965039775</v>
       </c>
       <c r="F10" s="10">
-        <v>0.75860410784332366</v>
+        <v>0.76011679752714267</v>
       </c>
       <c r="G10" s="10">
-        <v>0.82412408945459414</v>
+        <v>0.8252141888457406</v>
       </c>
       <c r="H10" s="10">
-        <v>-0.77627074293922116</v>
+        <v>-0.76623939438077782</v>
       </c>
       <c r="I10" s="10">
-        <v>0.28217030918479685</v>
+        <v>0.29704565373977965</v>
       </c>
       <c r="J10" s="10">
-        <v>0.29519072758087334</v>
+        <v>0.30589798619953257</v>
       </c>
       <c r="K10" s="10">
-        <v>-0.18771532289994133</v>
+        <v>-0.16644303580917458</v>
       </c>
       <c r="L10" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -14953,37 +15260,37 @@
         <v>143</v>
       </c>
       <c r="B37" s="10">
-        <v>0.83952547821423384</v>
+        <v>0.83478057131195182</v>
       </c>
       <c r="C37" s="10">
-        <v>-0.20550212529558737</v>
+        <v>-0.14610139618251997</v>
       </c>
       <c r="D37" s="10">
-        <v>0.73891073144504271</v>
+        <v>0.73342112013984695</v>
       </c>
       <c r="E37" s="10">
-        <v>0.89944427125544324</v>
+        <v>0.89365157060528466</v>
       </c>
       <c r="F37" s="10">
-        <v>0.84948306233457482</v>
+        <v>0.83887071985542006</v>
       </c>
       <c r="G37" s="10">
-        <v>0.82473133023925227</v>
+        <v>0.83006037903805296</v>
       </c>
       <c r="H37" s="10">
-        <v>-1.013099103138722</v>
+        <v>-0.91557668830660488</v>
       </c>
       <c r="I37" s="10">
-        <v>0.2994728031212025</v>
+        <v>0.37038902710883553</v>
       </c>
       <c r="J37" s="10">
-        <v>0.30026124625664663</v>
+        <v>0.35278343561478825</v>
       </c>
       <c r="K37" s="10">
-        <v>-0.292601867211852</v>
+        <v>-0.16526312289563605</v>
       </c>
       <c r="L37" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -14991,37 +15298,37 @@
         <v>0.15</v>
       </c>
       <c r="B38" s="10">
-        <v>0.83952547821423384</v>
+        <v>0.83478057131195182</v>
       </c>
       <c r="C38" s="10">
-        <v>-0.20550212529558737</v>
+        <v>-0.14610139618251997</v>
       </c>
       <c r="D38" s="10">
-        <v>0.73891073144504271</v>
+        <v>0.73342112013984695</v>
       </c>
       <c r="E38" s="10">
-        <v>0.89944427125544324</v>
+        <v>0.89365157060528466</v>
       </c>
       <c r="F38" s="10">
-        <v>0.84948306233457482</v>
+        <v>0.83887071985542006</v>
       </c>
       <c r="G38" s="10">
-        <v>0.82473133023925227</v>
+        <v>0.83006037903805296</v>
       </c>
       <c r="H38" s="10">
-        <v>-1.013099103138722</v>
+        <v>-0.91557668830660488</v>
       </c>
       <c r="I38" s="10">
-        <v>0.2994728031212025</v>
+        <v>0.37038902710883553</v>
       </c>
       <c r="J38" s="10">
-        <v>0.30026124625664663</v>
+        <v>0.35278343561478825</v>
       </c>
       <c r="K38" s="10">
-        <v>-0.292601867211852</v>
+        <v>-0.16526312289563605</v>
       </c>
       <c r="L38" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -15177,84 +15484,84 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
-        <v>1024</v>
+      <c r="A43" s="7">
+        <v>5</v>
       </c>
       <c r="B43" s="10">
-        <v>0.54507496754304918</v>
+        <v>0.81580094370282341</v>
       </c>
       <c r="C43" s="10">
-        <v>-0.14494785652419145</v>
+        <v>9.150152026974967E-2</v>
       </c>
       <c r="D43" s="10">
-        <v>0.35990404861370839</v>
+        <v>0.71146267491906379</v>
       </c>
       <c r="E43" s="10">
-        <v>0.71059100545035214</v>
+        <v>0.87048076800465024</v>
       </c>
       <c r="F43" s="10">
-        <v>0.47754947446814872</v>
+        <v>0.79642134993880132</v>
       </c>
       <c r="G43" s="10">
-        <v>0.70452761123883101</v>
+        <v>0.85137657423325541</v>
       </c>
       <c r="H43" s="10">
-        <v>-0.38864148321049863</v>
+        <v>-0.52548702897813637</v>
       </c>
       <c r="I43" s="10">
-        <v>8.9076829614158082E-2</v>
+        <v>0.6540539230593676</v>
       </c>
       <c r="J43" s="10">
-        <v>0.10018360224529324</v>
+        <v>0.56287219304735481</v>
       </c>
       <c r="K43" s="10">
-        <v>-0.15181867253603026</v>
+        <v>0.34409185436922768</v>
       </c>
       <c r="L43" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>91</v>
+      <c r="A44" s="3">
+        <v>1024</v>
       </c>
       <c r="B44" s="10">
-        <v>0.74924138854953315</v>
+        <v>0.54507496754304918</v>
       </c>
       <c r="C44" s="10">
-        <v>-8.849625864658725E-2</v>
+        <v>-0.14494785652419145</v>
       </c>
       <c r="D44" s="10">
-        <v>0.58934326207549126</v>
+        <v>0.35990404861370839</v>
       </c>
       <c r="E44" s="10">
-        <v>0.84860775551704504</v>
+        <v>0.71059100545035214</v>
       </c>
       <c r="F44" s="10">
-        <v>0.72233815881884555</v>
+        <v>0.47754947446814872</v>
       </c>
       <c r="G44" s="10">
-        <v>0.82639235656347443</v>
+        <v>0.70452761123883101</v>
       </c>
       <c r="H44" s="10">
-        <v>-0.51366844206920037</v>
+        <v>-0.38864148321049863</v>
       </c>
       <c r="I44" s="10">
-        <v>0.26025272902454277</v>
+        <v>8.9076829614158082E-2</v>
       </c>
       <c r="J44" s="10">
-        <v>0.26349721687193661</v>
+        <v>0.10018360224529324</v>
       </c>
       <c r="K44" s="10">
-        <v>-9.4443145194353414E-2</v>
+        <v>-0.15181867253603026</v>
       </c>
       <c r="L44" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
-        <v>0.1</v>
+      <c r="A45" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B45" s="10">
         <v>0.74924138854953315</v>
@@ -15291,76 +15598,76 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
-        <v>1</v>
+      <c r="A46" s="5">
+        <v>0.1</v>
       </c>
       <c r="B46" s="10">
-        <v>0.7687160329509809</v>
+        <v>0.74924138854953315</v>
       </c>
       <c r="C46" s="10">
-        <v>-0.1018973670859001</v>
+        <v>-8.849625864658725E-2</v>
       </c>
       <c r="D46" s="10">
-        <v>0.69700802149058638</v>
+        <v>0.58934326207549126</v>
       </c>
       <c r="E46" s="10">
-        <v>0.83890398810674194</v>
+        <v>0.84860775551704504</v>
       </c>
       <c r="F46" s="10">
-        <v>0.67893628865697231</v>
+        <v>0.72233815881884555</v>
       </c>
       <c r="G46" s="10">
-        <v>0.85066045471301566</v>
+        <v>0.82639235656347443</v>
       </c>
       <c r="H46" s="10">
-        <v>-0.67261580953703159</v>
+        <v>-0.51366844206920037</v>
       </c>
       <c r="I46" s="10">
-        <v>0.30848244788702678</v>
+        <v>0.26025272902454277</v>
       </c>
       <c r="J46" s="10">
-        <v>0.31495528196096989</v>
+        <v>0.26349721687193661</v>
       </c>
       <c r="K46" s="10">
-        <v>-6.2549910870268954E-2</v>
+        <v>-9.4443145194353414E-2</v>
       </c>
       <c r="L46" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" s="10">
-        <v>0.79442331710326963</v>
+        <v>0.7687160329509809</v>
       </c>
       <c r="C47" s="10">
-        <v>0.18890428306448309</v>
+        <v>-0.1018973670859001</v>
       </c>
       <c r="D47" s="10">
-        <v>0.69461192756619639</v>
+        <v>0.69700802149058638</v>
       </c>
       <c r="E47" s="10">
-        <v>0.87843299561426591</v>
+        <v>0.83890398810674194</v>
       </c>
       <c r="F47" s="10">
-        <v>0.76870774427119959</v>
+        <v>0.67893628865697231</v>
       </c>
       <c r="G47" s="10">
-        <v>0.8657777210859523</v>
+        <v>0.85066045471301566</v>
       </c>
       <c r="H47" s="10">
-        <v>0.2442860439736072</v>
+        <v>-0.67261580953703159</v>
       </c>
       <c r="I47" s="10">
-        <v>0.27498782728922072</v>
+        <v>0.30848244788702678</v>
       </c>
       <c r="J47" s="10">
-        <v>0.31344779846252901</v>
+        <v>0.31495528196096989</v>
       </c>
       <c r="K47" s="10">
-        <v>0.20383816913817321</v>
+        <v>-6.2549910870268954E-2</v>
       </c>
       <c r="L47" s="10">
         <v>1</v>
@@ -15368,37 +15675,37 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" s="10">
-        <v>0.76288008972886723</v>
+        <v>0.79442331710326963</v>
       </c>
       <c r="C48" s="10">
-        <v>-0.2346253602248935</v>
+        <v>0.18890428306448309</v>
       </c>
       <c r="D48" s="10">
-        <v>0.56217227264353165</v>
+        <v>0.69461192756619639</v>
       </c>
       <c r="E48" s="10">
-        <v>0.8860302856604424</v>
+        <v>0.87843299561426591</v>
       </c>
       <c r="F48" s="10">
-        <v>0.8193006606391926</v>
+        <v>0.76870774427119959</v>
       </c>
       <c r="G48" s="10">
-        <v>0.82516830197440383</v>
+        <v>0.8657777210859523</v>
       </c>
       <c r="H48" s="10">
-        <v>-0.68138424664239317</v>
+        <v>0.2442860439736072</v>
       </c>
       <c r="I48" s="10">
-        <v>0.26100581310338711</v>
+        <v>0.27498782728922072</v>
       </c>
       <c r="J48" s="10">
-        <v>0.19683381507042591</v>
+        <v>0.31344779846252901</v>
       </c>
       <c r="K48" s="10">
-        <v>-0.32598079507706462</v>
+        <v>0.20383816913817321</v>
       </c>
       <c r="L48" s="10">
         <v>1</v>
@@ -15406,37 +15713,37 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" s="10">
-        <v>0.76118150293457421</v>
+        <v>0.76288008972886723</v>
       </c>
       <c r="C49" s="10">
-        <v>-0.18115312472614889</v>
+        <v>-0.2346253602248935</v>
       </c>
       <c r="D49" s="10">
-        <v>0.62772005551197863</v>
+        <v>0.56217227264353165</v>
       </c>
       <c r="E49" s="10">
-        <v>0.83191185108329491</v>
+        <v>0.8860302856604424</v>
       </c>
       <c r="F49" s="10">
-        <v>0.6996564818337313</v>
+        <v>0.8193006606391926</v>
       </c>
       <c r="G49" s="10">
-        <v>0.77588049834428796</v>
+        <v>0.82516830197440383</v>
       </c>
       <c r="H49" s="10">
-        <v>-1.1287324429254719</v>
+        <v>-0.68138424664239317</v>
       </c>
       <c r="I49" s="10">
-        <v>0.52018665256350383</v>
+        <v>0.26100581310338711</v>
       </c>
       <c r="J49" s="10">
-        <v>0.53041945251480216</v>
+        <v>0.19683381507042591</v>
       </c>
       <c r="K49" s="10">
-        <v>-7.7928630103461183E-2</v>
+        <v>-0.32598079507706462</v>
       </c>
       <c r="L49" s="10">
         <v>1</v>
@@ -15444,83 +15751,83 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B50" s="10">
-        <v>0.65900600002997334</v>
+        <v>0.76118150293457421</v>
       </c>
       <c r="C50" s="10">
-        <v>-0.1137097242604768</v>
+        <v>-0.18115312472614889</v>
       </c>
       <c r="D50" s="10">
-        <v>0.36520403316516331</v>
+        <v>0.62772005551197863</v>
       </c>
       <c r="E50" s="10">
-        <v>0.80775965712048059</v>
+        <v>0.83191185108329491</v>
       </c>
       <c r="F50" s="10">
-        <v>0.64508961869313208</v>
+        <v>0.6996564818337313</v>
       </c>
       <c r="G50" s="10">
-        <v>0.81447480669971251</v>
+        <v>0.77588049834428796</v>
       </c>
       <c r="H50" s="10">
-        <v>-0.32989575521471209</v>
+        <v>-1.1287324429254719</v>
       </c>
       <c r="I50" s="10">
-        <v>-6.3399095720424459E-2</v>
+        <v>0.52018665256350383</v>
       </c>
       <c r="J50" s="10">
-        <v>-3.8170263649043967E-2</v>
+        <v>0.53041945251480216</v>
       </c>
       <c r="K50" s="10">
-        <v>-0.20959455905914551</v>
+        <v>-7.7928630103461183E-2</v>
       </c>
       <c r="L50" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>133</v>
+      <c r="A51" s="7">
+        <v>5</v>
       </c>
       <c r="B51" s="10">
-        <v>0.34090854653656527</v>
+        <v>0.65900600002997334</v>
       </c>
       <c r="C51" s="10">
-        <v>-0.20139945440179563</v>
+        <v>-0.1137097242604768</v>
       </c>
       <c r="D51" s="10">
-        <v>0.13046483515192558</v>
+        <v>0.36520403316516331</v>
       </c>
       <c r="E51" s="10">
-        <v>0.57257425538365925</v>
+        <v>0.80775965712048059</v>
       </c>
       <c r="F51" s="10">
-        <v>0.23276079011745207</v>
+        <v>0.64508961869313208</v>
       </c>
       <c r="G51" s="10">
-        <v>0.58266286591418781</v>
+        <v>0.81447480669971251</v>
       </c>
       <c r="H51" s="10">
-        <v>-0.26361452435179689</v>
+        <v>-0.32989575521471209</v>
       </c>
       <c r="I51" s="10">
-        <v>-8.2099069796226637E-2</v>
+        <v>-6.3399095720424459E-2</v>
       </c>
       <c r="J51" s="10">
-        <v>-6.3130012381350117E-2</v>
+        <v>-3.8170263649043967E-2</v>
       </c>
       <c r="K51" s="10">
-        <v>-0.2091941998777071</v>
+        <v>-0.20959455905914551</v>
       </c>
       <c r="L51" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
-        <v>0.05</v>
+      <c r="A52" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="B52" s="10">
         <v>0.34090854653656527</v>
@@ -15557,76 +15864,76 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>1</v>
+      <c r="A53" s="5">
+        <v>0.05</v>
       </c>
       <c r="B53" s="10">
-        <v>0.36236966024911332</v>
+        <v>0.34090854653656527</v>
       </c>
       <c r="C53" s="10">
-        <v>-0.2203559043159494</v>
+        <v>-0.20139945440179563</v>
       </c>
       <c r="D53" s="10">
-        <v>0.21221737882565619</v>
+        <v>0.13046483515192558</v>
       </c>
       <c r="E53" s="10">
-        <v>0.5433972549649968</v>
+        <v>0.57257425538365925</v>
       </c>
       <c r="F53" s="10">
-        <v>0.1798672964141548</v>
+        <v>0.23276079011745207</v>
       </c>
       <c r="G53" s="10">
-        <v>0.69610748218738094</v>
+        <v>0.58266286591418781</v>
       </c>
       <c r="H53" s="10">
-        <v>-0.39082763040243362</v>
+        <v>-0.26361452435179689</v>
       </c>
       <c r="I53" s="10">
-        <v>-5.9943945711704361E-2</v>
+        <v>-8.2099069796226637E-2</v>
       </c>
       <c r="J53" s="10">
-        <v>-9.2893487104375616E-2</v>
+        <v>-6.3130012381350117E-2</v>
       </c>
       <c r="K53" s="10">
-        <v>-0.22449729398133139</v>
+        <v>-0.2091941998777071</v>
       </c>
       <c r="L53" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="10">
-        <v>0.36730705242407818</v>
+        <v>0.36236966024911332</v>
       </c>
       <c r="C54" s="10">
-        <v>-0.18502663943294051</v>
+        <v>-0.2203559043159494</v>
       </c>
       <c r="D54" s="10">
-        <v>0.19814482058725269</v>
+        <v>0.21221737882565619</v>
       </c>
       <c r="E54" s="10">
-        <v>0.63902400539696647</v>
+        <v>0.5433972549649968</v>
       </c>
       <c r="F54" s="10">
-        <v>0.18398279220589681</v>
+        <v>0.1798672964141548</v>
       </c>
       <c r="G54" s="10">
-        <v>0.63182416593721968</v>
+        <v>0.69610748218738094</v>
       </c>
       <c r="H54" s="10">
-        <v>-0.21149501268980539</v>
+        <v>-0.39082763040243362</v>
       </c>
       <c r="I54" s="10">
-        <v>-0.1158541526438668</v>
+        <v>-5.9943945711704361E-2</v>
       </c>
       <c r="J54" s="10">
-        <v>-0.142929672603894</v>
+        <v>-9.2893487104375616E-2</v>
       </c>
       <c r="K54" s="10">
-        <v>-5.3946416691347247E-2</v>
+        <v>-0.22449729398133139</v>
       </c>
       <c r="L54" s="10">
         <v>1</v>
@@ -15634,37 +15941,37 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" s="10">
-        <v>0.30908052594271451</v>
+        <v>0.36730705242407818</v>
       </c>
       <c r="C55" s="10">
-        <v>-0.25846877494804849</v>
+        <v>-0.18502663943294051</v>
       </c>
       <c r="D55" s="10">
-        <v>0.13574346461914649</v>
+        <v>0.19814482058725269</v>
       </c>
       <c r="E55" s="10">
-        <v>0.60187189283430609</v>
+        <v>0.63902400539696647</v>
       </c>
       <c r="F55" s="10">
-        <v>0.21583975245046169</v>
+        <v>0.18398279220589681</v>
       </c>
       <c r="G55" s="10">
-        <v>0.52511659288826185</v>
+        <v>0.63182416593721968</v>
       </c>
       <c r="H55" s="10">
-        <v>-0.33036074734245952</v>
+        <v>-0.21149501268980539</v>
       </c>
       <c r="I55" s="10">
-        <v>-3.5325060111648147E-2</v>
+        <v>-0.1158541526438668</v>
       </c>
       <c r="J55" s="10">
-        <v>-1.97031750299963E-2</v>
+        <v>-0.142929672603894</v>
       </c>
       <c r="K55" s="10">
-        <v>-0.37479497702385262</v>
+        <v>-5.3946416691347247E-2</v>
       </c>
       <c r="L55" s="10">
         <v>1</v>
@@ -15672,37 +15979,37 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="10">
-        <v>0.36397912468366639</v>
+        <v>0.30908052594271451</v>
       </c>
       <c r="C56" s="10">
-        <v>-0.1168826118850578</v>
+        <v>-0.25846877494804849</v>
       </c>
       <c r="D56" s="10">
-        <v>0.19785684542918791</v>
+        <v>0.13574346461914649</v>
       </c>
       <c r="E56" s="10">
-        <v>0.53991517975978209</v>
+        <v>0.60187189283430609</v>
       </c>
       <c r="F56" s="10">
-        <v>0.28724917217649659</v>
+        <v>0.21583975245046169</v>
       </c>
       <c r="G56" s="10">
-        <v>0.53079985956210807</v>
+        <v>0.52511659288826185</v>
       </c>
       <c r="H56" s="10">
-        <v>-0.24212628071734391</v>
+        <v>-0.33036074734245952</v>
       </c>
       <c r="I56" s="10">
-        <v>-6.3695226693954998E-2</v>
+        <v>-3.5325060111648147E-2</v>
       </c>
       <c r="J56" s="10">
-        <v>-1.614183840791128E-2</v>
+        <v>-1.97031750299963E-2</v>
       </c>
       <c r="K56" s="10">
-        <v>-4.6905790899782973E-2</v>
+        <v>-0.37479497702385262</v>
       </c>
       <c r="L56" s="10">
         <v>1</v>
@@ -15710,78 +16017,116 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B57" s="10">
-        <v>0.30180636938325411</v>
+        <v>0.36397912468366639</v>
       </c>
       <c r="C57" s="10">
-        <v>-0.22626334142698201</v>
+        <v>-0.1168826118850578</v>
       </c>
       <c r="D57" s="10">
-        <v>-9.1638333701615338E-2</v>
+        <v>0.19785684542918791</v>
       </c>
       <c r="E57" s="10">
-        <v>0.53866294396224468</v>
+        <v>0.53991517975978209</v>
       </c>
       <c r="F57" s="10">
-        <v>0.29686493734025049</v>
+        <v>0.28724917217649659</v>
       </c>
       <c r="G57" s="10">
-        <v>0.5294662289959684</v>
+        <v>0.53079985956210807</v>
       </c>
       <c r="H57" s="10">
-        <v>-0.14326295060694211</v>
+        <v>-0.24212628071734391</v>
       </c>
       <c r="I57" s="10">
-        <v>-0.13567696381995889</v>
+        <v>-6.3695226693954998E-2</v>
       </c>
       <c r="J57" s="10">
-        <v>-4.3981888760573407E-2</v>
+        <v>-1.614183840791128E-2</v>
       </c>
       <c r="K57" s="10">
-        <v>-0.34582652079222131</v>
+        <v>-4.6905790899782973E-2</v>
       </c>
       <c r="L57" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="7">
+        <v>5</v>
+      </c>
+      <c r="B58" s="10">
+        <v>0.30180636938325411</v>
+      </c>
+      <c r="C58" s="10">
+        <v>-0.22626334142698201</v>
+      </c>
+      <c r="D58" s="10">
+        <v>-9.1638333701615338E-2</v>
+      </c>
+      <c r="E58" s="10">
+        <v>0.53866294396224468</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0.29686493734025049</v>
+      </c>
+      <c r="G58" s="10">
+        <v>0.5294662289959684</v>
+      </c>
+      <c r="H58" s="10">
+        <v>-0.14326295060694211</v>
+      </c>
+      <c r="I58" s="10">
+        <v>-0.13567696381995889</v>
+      </c>
+      <c r="J58" s="10">
+        <v>-4.3981888760573407E-2</v>
+      </c>
+      <c r="K58" s="10">
+        <v>-0.34582652079222131</v>
+      </c>
+      <c r="L58" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="10">
-        <v>0.71148093964611814</v>
-      </c>
-      <c r="C58" s="10">
-        <v>-0.1066240662859597</v>
-      </c>
-      <c r="D58" s="10">
-        <v>0.55094275233866719</v>
-      </c>
-      <c r="E58" s="10">
-        <v>0.82003211215111838</v>
-      </c>
-      <c r="F58" s="10">
-        <v>0.68166350588596503</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0.7935650893908891</v>
-      </c>
-      <c r="H58" s="10">
-        <v>-0.63965864203445855</v>
-      </c>
-      <c r="I58" s="10">
-        <v>0.23449660743379469</v>
-      </c>
-      <c r="J58" s="10">
-        <v>0.24558480078848269</v>
-      </c>
-      <c r="K58" s="10">
-        <v>-0.1695360134400038</v>
-      </c>
-      <c r="L58" s="10">
-        <v>39</v>
+      <c r="B59" s="10">
+        <v>0.71408893974753562</v>
+      </c>
+      <c r="C59" s="10">
+        <v>-0.10167092662206698</v>
+      </c>
+      <c r="D59" s="10">
+        <v>0.55495575040317713</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.82129332854745685</v>
+      </c>
+      <c r="F59" s="10">
+        <v>0.68453245198728596</v>
+      </c>
+      <c r="G59" s="10">
+        <v>0.79501037651194828</v>
+      </c>
+      <c r="H59" s="10">
+        <v>-0.6368043517080505</v>
+      </c>
+      <c r="I59" s="10">
+        <v>0.24498554032443401</v>
+      </c>
+      <c r="J59" s="10">
+        <v>0.2535169855949545</v>
+      </c>
+      <c r="K59" s="10">
+        <v>-0.15669531674477302</v>
+      </c>
+      <c r="L59" s="10">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/Final_winner_optimization.xlsx
+++ b/logs/final_winner_optimization/Final_winner_optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/final_winner_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D32870F-A697-4718-B2CA-DB35766B3358}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B00E18A-8DE8-4B35-BA93-E267AE6C2AEA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="151">
   <si>
     <t>date</t>
   </si>
@@ -474,6 +474,15 @@
   <si>
     <t>03-02_05-07-38_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
   </si>
+  <si>
+    <t>03-02_12-37-47_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
+  <si>
+    <t>[0.03, 0.003]</t>
+  </si>
+  <si>
+    <t>03-02_23-08-35_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -617,13 +626,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46083.677971064812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46084.432343055552" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="42" xr:uid="{D08D57CE-FB90-42B1-BBC2-2529582820EE}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-02T05:07:38"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-16T18:21:04" maxDate="2026-03-02T23:08:35"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -713,27 +722,30 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="batch_size" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="256" maxValue="1024" count="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="256" maxValue="1024" count="4">
         <n v="512"/>
         <n v="256"/>
         <n v="1024"/>
+        <n v="768"/>
       </sharedItems>
     </cacheField>
     <cacheField name="learning_rate" numFmtId="0">
-      <sharedItems count="4">
+      <sharedItems count="5">
         <s v="[0.05, 0.001]"/>
         <s v="[0.1, 0.005]"/>
         <s v="[0.01, 0.0005]"/>
         <s v="[0.1, 0.001]"/>
+        <s v="[0.03, 0.003]"/>
       </sharedItems>
     </cacheField>
     <cacheField name="perturbation" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.05" maxValue="0.25" count="5">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.05" maxValue="0.25" count="6">
         <n v="0.1"/>
         <n v="0.2"/>
         <n v="0.05"/>
         <n v="0.25"/>
         <n v="0.15"/>
+        <n v="0.12"/>
       </sharedItems>
     </cacheField>
     <cacheField name="total params" numFmtId="0">
@@ -878,7 +890,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="42">
   <r>
     <d v="2026-02-16T18:21:04"/>
     <s v="02-16_18-21-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
@@ -3959,12 +3971,166 @@
     <n v="230.45239689593109"/>
     <n v="0.34409185436922768"/>
   </r>
+  <r>
+    <d v="2026-03-02T12:37:47"/>
+    <s v="03-02_12-37-47_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="0.10668381337577899"/>
+    <n v="12.148959099296221"/>
+    <n v="0.68937919081156052"/>
+    <n v="-0.15503891623588789"/>
+    <n v="14.902914769640439"/>
+    <n v="0.69711428884943683"/>
+    <n v="14.902914769640439"/>
+    <n v="14.902914769640439"/>
+    <n v="0.69711428884943683"/>
+    <n v="84.093001474728794"/>
+    <n v="-4.8602094735892387E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="5.8718713735268671E-2"/>
+    <n v="0.5736262174198179"/>
+    <n v="5.8718713735268671E-2"/>
+    <n v="5.8718713735268671E-2"/>
+    <n v="0.5736262174198179"/>
+    <n v="0.22850283325169249"/>
+    <n v="-0.65922601409598025"/>
+    <n v="5.5391996374860787E-2"/>
+    <n v="0.80807856329507688"/>
+    <n v="5.5391996374860787E-2"/>
+    <n v="5.5391996374860787E-2"/>
+    <n v="0.80807856329507688"/>
+    <n v="0.22712103552482971"/>
+    <n v="0.21307412087393371"/>
+    <n v="0.1056640784052614"/>
+    <n v="0.57579214695214831"/>
+    <n v="0.1056640784052614"/>
+    <n v="0.1056640784052614"/>
+    <n v="0.57579214695214831"/>
+    <n v="0.19746045121170319"/>
+    <n v="0.2072587455018606"/>
+    <n v="59.391884290046463"/>
+    <n v="0.83096022773070333"/>
+    <n v="59.391884290046463"/>
+    <n v="59.391884290046463"/>
+    <n v="0.83096022773070333"/>
+    <n v="335.71892157892643"/>
+    <n v="4.4484768776626327E-2"/>
+  </r>
+  <r>
+    <d v="2026-03-02T23:08:35"/>
+    <s v="03-02_23-08-35_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <n v="3"/>
+    <s v="compact"/>
+    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+    <s v="full"/>
+    <s v="[2, 3, 2]"/>
+    <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="180"/>
+    <n v="60"/>
+    <n v="120"/>
+    <n v="9.8884822278996115E-2"/>
+    <n v="11.876573186006681"/>
+    <n v="0.71885512298387355"/>
+    <n v="-3.2782694628944981E-2"/>
+    <n v="14.467629636685389"/>
+    <n v="0.72886677138809031"/>
+    <n v="14.467629636685389"/>
+    <n v="14.467629636685389"/>
+    <n v="0.72886677138809031"/>
+    <n v="88.190072077096303"/>
+    <n v="6.5826158779917376E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="5.3515425749245983E-2"/>
+    <n v="0.61140881583395812"/>
+    <n v="5.3515425749245983E-2"/>
+    <n v="5.3515425749245983E-2"/>
+    <n v="0.61140881583395812"/>
+    <n v="0.1164453542986079"/>
+    <n v="0.15445616877731899"/>
+    <n v="4.1214087084029523E-2"/>
+    <n v="0.85720199084143156"/>
+    <n v="4.1214087084029523E-2"/>
+    <n v="4.1214087084029523E-2"/>
+    <n v="0.85720199084143156"/>
+    <n v="0.2626723747824426"/>
+    <n v="8.9896323472831163E-2"/>
+    <n v="9.6889178268984202E-2"/>
+    <n v="0.61102059548167342"/>
+    <n v="9.6889178268984202E-2"/>
+    <n v="9.6889178268984202E-2"/>
+    <n v="0.61102059548167342"/>
+    <n v="0.24380571813241941"/>
+    <n v="2.1197157911392539E-2"/>
+    <n v="57.678899855639273"/>
+    <n v="0.83583568339530101"/>
+    <n v="57.678899855639273"/>
+    <n v="57.678899855639273"/>
+    <n v="0.83583568339530101"/>
+    <n v="352.13736486117199"/>
+    <n v="-2.2450150418724668E-3"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24326305-70A8-4C78-9FE9-6DC3DEA8AA33}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:L59" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A1:L64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -4004,17 +4170,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
+      <items count="5">
         <item x="1"/>
         <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item t="default"/>
@@ -4022,11 +4180,22 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
         <item x="2"/>
         <item x="0"/>
         <item x="1"/>
         <item x="3"/>
         <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4081,7 +4250,7 @@
     <field x="30"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="58">
+  <rowItems count="63">
     <i>
       <x/>
     </i>
@@ -4253,6 +4422,21 @@
     <i r="3">
       <x v="4"/>
     </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -4321,7 +4505,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW41" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FD8B8E0-7297-488B-B165-DA6A36FEBC27}" name="Tabla1" displayName="Tabla1" ref="A1:BW43" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <tableColumns count="75">
     <tableColumn id="1" xr3:uid="{E29847FD-796C-4D7F-957B-1B478BBCCC1D}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{AFC0F8DD-B9EA-4787-891C-59254C048BBB}" name="model_id"/>
@@ -4666,7 +4850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW41"/>
+  <dimension ref="A1:BW43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="42" max="42" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -13858,6 +14042,454 @@
       </c>
       <c r="BW41">
         <v>0.34409185436922768</v>
+      </c>
+    </row>
+    <row r="42" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46083.526238425933</v>
+      </c>
+      <c r="B42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42">
+        <v>16590</v>
+      </c>
+      <c r="G42">
+        <v>4.5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s">
+        <v>79</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42" t="s">
+        <v>80</v>
+      </c>
+      <c r="M42" t="s">
+        <v>81</v>
+      </c>
+      <c r="N42" t="s">
+        <v>82</v>
+      </c>
+      <c r="O42" t="s">
+        <v>82</v>
+      </c>
+      <c r="P42" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>84</v>
+      </c>
+      <c r="R42">
+        <v>3</v>
+      </c>
+      <c r="S42" t="s">
+        <v>85</v>
+      </c>
+      <c r="T42" t="s">
+        <v>86</v>
+      </c>
+      <c r="U42" t="s">
+        <v>87</v>
+      </c>
+      <c r="V42" t="s">
+        <v>88</v>
+      </c>
+      <c r="W42" t="s">
+        <v>89</v>
+      </c>
+      <c r="X42" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z42">
+        <v>4000</v>
+      </c>
+      <c r="AA42">
+        <v>4000</v>
+      </c>
+      <c r="AC42">
+        <v>768</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE42">
+        <v>0.12</v>
+      </c>
+      <c r="AF42">
+        <v>180</v>
+      </c>
+      <c r="AG42">
+        <v>60</v>
+      </c>
+      <c r="AH42">
+        <v>120</v>
+      </c>
+      <c r="AI42">
+        <v>0.10668381337577899</v>
+      </c>
+      <c r="AJ42">
+        <v>12.148959099296221</v>
+      </c>
+      <c r="AK42">
+        <v>0.68937919081156052</v>
+      </c>
+      <c r="AL42">
+        <v>-0.15503891623588789</v>
+      </c>
+      <c r="AM42">
+        <v>14.902914769640439</v>
+      </c>
+      <c r="AN42">
+        <v>0.69711428884943683</v>
+      </c>
+      <c r="AO42">
+        <v>14.902914769640439</v>
+      </c>
+      <c r="AP42">
+        <v>14.902914769640439</v>
+      </c>
+      <c r="AQ42">
+        <v>0.69711428884943683</v>
+      </c>
+      <c r="AR42">
+        <v>84.093001474728794</v>
+      </c>
+      <c r="AS42">
+        <v>-4.8602094735892387E-2</v>
+      </c>
+      <c r="AT42">
+        <v>0.8</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV42">
+        <v>5.8718713735268671E-2</v>
+      </c>
+      <c r="AW42">
+        <v>0.5736262174198179</v>
+      </c>
+      <c r="AX42">
+        <v>5.8718713735268671E-2</v>
+      </c>
+      <c r="AY42">
+        <v>5.8718713735268671E-2</v>
+      </c>
+      <c r="AZ42">
+        <v>0.5736262174198179</v>
+      </c>
+      <c r="BA42">
+        <v>0.22850283325169249</v>
+      </c>
+      <c r="BB42">
+        <v>-0.65922601409598025</v>
+      </c>
+      <c r="BC42">
+        <v>5.5391996374860787E-2</v>
+      </c>
+      <c r="BD42">
+        <v>0.80807856329507688</v>
+      </c>
+      <c r="BE42">
+        <v>5.5391996374860787E-2</v>
+      </c>
+      <c r="BF42">
+        <v>5.5391996374860787E-2</v>
+      </c>
+      <c r="BG42">
+        <v>0.80807856329507688</v>
+      </c>
+      <c r="BH42">
+        <v>0.22712103552482971</v>
+      </c>
+      <c r="BI42">
+        <v>0.21307412087393371</v>
+      </c>
+      <c r="BJ42">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BK42">
+        <v>0.57579214695214831</v>
+      </c>
+      <c r="BL42">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BM42">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BN42">
+        <v>0.57579214695214831</v>
+      </c>
+      <c r="BO42">
+        <v>0.19746045121170319</v>
+      </c>
+      <c r="BP42">
+        <v>0.2072587455018606</v>
+      </c>
+      <c r="BQ42">
+        <v>59.391884290046463</v>
+      </c>
+      <c r="BR42">
+        <v>0.83096022773070333</v>
+      </c>
+      <c r="BS42">
+        <v>59.391884290046463</v>
+      </c>
+      <c r="BT42">
+        <v>59.391884290046463</v>
+      </c>
+      <c r="BU42">
+        <v>0.83096022773070333</v>
+      </c>
+      <c r="BV42">
+        <v>335.71892157892643</v>
+      </c>
+      <c r="BW42">
+        <v>4.4484768776626327E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46083.96429398148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43">
+        <v>16590</v>
+      </c>
+      <c r="G43">
+        <v>4.5</v>
+      </c>
+      <c r="H43" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s">
+        <v>79</v>
+      </c>
+      <c r="J43">
+        <v>5</v>
+      </c>
+      <c r="K43">
+        <v>5</v>
+      </c>
+      <c r="L43" t="s">
+        <v>80</v>
+      </c>
+      <c r="M43" t="s">
+        <v>81</v>
+      </c>
+      <c r="N43" t="s">
+        <v>82</v>
+      </c>
+      <c r="O43" t="s">
+        <v>82</v>
+      </c>
+      <c r="P43" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>84</v>
+      </c>
+      <c r="R43">
+        <v>3</v>
+      </c>
+      <c r="S43" t="s">
+        <v>85</v>
+      </c>
+      <c r="T43" t="s">
+        <v>86</v>
+      </c>
+      <c r="U43" t="s">
+        <v>87</v>
+      </c>
+      <c r="V43" t="s">
+        <v>88</v>
+      </c>
+      <c r="W43" t="s">
+        <v>89</v>
+      </c>
+      <c r="X43" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z43">
+        <v>4000</v>
+      </c>
+      <c r="AA43">
+        <v>4000</v>
+      </c>
+      <c r="AC43">
+        <v>768</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE43">
+        <v>0.12</v>
+      </c>
+      <c r="AF43">
+        <v>180</v>
+      </c>
+      <c r="AG43">
+        <v>60</v>
+      </c>
+      <c r="AH43">
+        <v>120</v>
+      </c>
+      <c r="AI43">
+        <v>9.8884822278996115E-2</v>
+      </c>
+      <c r="AJ43">
+        <v>11.876573186006681</v>
+      </c>
+      <c r="AK43">
+        <v>0.71885512298387355</v>
+      </c>
+      <c r="AL43">
+        <v>-3.2782694628944981E-2</v>
+      </c>
+      <c r="AM43">
+        <v>14.467629636685389</v>
+      </c>
+      <c r="AN43">
+        <v>0.72886677138809031</v>
+      </c>
+      <c r="AO43">
+        <v>14.467629636685389</v>
+      </c>
+      <c r="AP43">
+        <v>14.467629636685389</v>
+      </c>
+      <c r="AQ43">
+        <v>0.72886677138809031</v>
+      </c>
+      <c r="AR43">
+        <v>88.190072077096303</v>
+      </c>
+      <c r="AS43">
+        <v>6.5826158779917376E-2</v>
+      </c>
+      <c r="AT43">
+        <v>0.8</v>
+      </c>
+      <c r="AU43" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV43">
+        <v>5.3515425749245983E-2</v>
+      </c>
+      <c r="AW43">
+        <v>0.61140881583395812</v>
+      </c>
+      <c r="AX43">
+        <v>5.3515425749245983E-2</v>
+      </c>
+      <c r="AY43">
+        <v>5.3515425749245983E-2</v>
+      </c>
+      <c r="AZ43">
+        <v>0.61140881583395812</v>
+      </c>
+      <c r="BA43">
+        <v>0.1164453542986079</v>
+      </c>
+      <c r="BB43">
+        <v>0.15445616877731899</v>
+      </c>
+      <c r="BC43">
+        <v>4.1214087084029523E-2</v>
+      </c>
+      <c r="BD43">
+        <v>0.85720199084143156</v>
+      </c>
+      <c r="BE43">
+        <v>4.1214087084029523E-2</v>
+      </c>
+      <c r="BF43">
+        <v>4.1214087084029523E-2</v>
+      </c>
+      <c r="BG43">
+        <v>0.85720199084143156</v>
+      </c>
+      <c r="BH43">
+        <v>0.2626723747824426</v>
+      </c>
+      <c r="BI43">
+        <v>8.9896323472831163E-2</v>
+      </c>
+      <c r="BJ43">
+        <v>9.6889178268984202E-2</v>
+      </c>
+      <c r="BK43">
+        <v>0.61102059548167342</v>
+      </c>
+      <c r="BL43">
+        <v>9.6889178268984202E-2</v>
+      </c>
+      <c r="BM43">
+        <v>9.6889178268984202E-2</v>
+      </c>
+      <c r="BN43">
+        <v>0.61102059548167342</v>
+      </c>
+      <c r="BO43">
+        <v>0.24380571813241941</v>
+      </c>
+      <c r="BP43">
+        <v>2.1197157911392539E-2</v>
+      </c>
+      <c r="BQ43">
+        <v>57.678899855639273</v>
+      </c>
+      <c r="BR43">
+        <v>0.83583568339530101</v>
+      </c>
+      <c r="BS43">
+        <v>57.678899855639273</v>
+      </c>
+      <c r="BT43">
+        <v>57.678899855639273</v>
+      </c>
+      <c r="BU43">
+        <v>0.83583568339530101</v>
+      </c>
+      <c r="BV43">
+        <v>352.13736486117199</v>
+      </c>
+      <c r="BW43">
+        <v>-2.2450150418724668E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13870,7 +14502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72AEA6F4-3101-46CE-BC02-B01BACDA33CE}">
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -16092,41 +16724,231 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="3">
+        <v>768</v>
+      </c>
+      <c r="B59" s="10">
+        <v>0.70411715689771703</v>
+      </c>
+      <c r="C59" s="10">
+        <v>-9.3910805432416436E-2</v>
+      </c>
+      <c r="D59" s="10">
+        <v>0.59251751662688801</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.83264027706825416</v>
+      </c>
+      <c r="F59" s="10">
+        <v>0.59340637121691087</v>
+      </c>
+      <c r="G59" s="10">
+        <v>0.83339795556300222</v>
+      </c>
+      <c r="H59" s="10">
+        <v>-0.25238492265933066</v>
+      </c>
+      <c r="I59" s="10">
+        <v>0.15148522217338245</v>
+      </c>
+      <c r="J59" s="10">
+        <v>0.11422795170662657</v>
+      </c>
+      <c r="K59" s="10">
+        <v>2.111987686737693E-2</v>
+      </c>
+      <c r="L59" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="10">
+        <v>0.70411715689771703</v>
+      </c>
+      <c r="C60" s="10">
+        <v>-9.3910805432416436E-2</v>
+      </c>
+      <c r="D60" s="10">
+        <v>0.59251751662688801</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.83264027706825416</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0.59340637121691087</v>
+      </c>
+      <c r="G60" s="10">
+        <v>0.83339795556300222</v>
+      </c>
+      <c r="H60" s="10">
+        <v>-0.25238492265933066</v>
+      </c>
+      <c r="I60" s="10">
+        <v>0.15148522217338245</v>
+      </c>
+      <c r="J60" s="10">
+        <v>0.11422795170662657</v>
+      </c>
+      <c r="K60" s="10">
+        <v>2.111987686737693E-2</v>
+      </c>
+      <c r="L60" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="B61" s="10">
+        <v>0.70411715689771703</v>
+      </c>
+      <c r="C61" s="10">
+        <v>-9.3910805432416436E-2</v>
+      </c>
+      <c r="D61" s="10">
+        <v>0.59251751662688801</v>
+      </c>
+      <c r="E61" s="10">
+        <v>0.83264027706825416</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0.59340637121691087</v>
+      </c>
+      <c r="G61" s="10">
+        <v>0.83339795556300222</v>
+      </c>
+      <c r="H61" s="10">
+        <v>-0.25238492265933066</v>
+      </c>
+      <c r="I61" s="10">
+        <v>0.15148522217338245</v>
+      </c>
+      <c r="J61" s="10">
+        <v>0.11422795170662657</v>
+      </c>
+      <c r="K61" s="10">
+        <v>2.111987686737693E-2</v>
+      </c>
+      <c r="L61" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="7">
+        <v>1</v>
+      </c>
+      <c r="B62" s="10">
+        <v>0.68937919081156052</v>
+      </c>
+      <c r="C62" s="10">
+        <v>-0.15503891623588789</v>
+      </c>
+      <c r="D62" s="10">
+        <v>0.5736262174198179</v>
+      </c>
+      <c r="E62" s="10">
+        <v>0.80807856329507688</v>
+      </c>
+      <c r="F62" s="10">
+        <v>0.57579214695214831</v>
+      </c>
+      <c r="G62" s="10">
+        <v>0.83096022773070333</v>
+      </c>
+      <c r="H62" s="10">
+        <v>-0.65922601409598025</v>
+      </c>
+      <c r="I62" s="10">
+        <v>0.21307412087393371</v>
+      </c>
+      <c r="J62" s="10">
+        <v>0.2072587455018606</v>
+      </c>
+      <c r="K62" s="10">
+        <v>4.4484768776626327E-2</v>
+      </c>
+      <c r="L62" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="7">
+        <v>2</v>
+      </c>
+      <c r="B63" s="10">
+        <v>0.71885512298387355</v>
+      </c>
+      <c r="C63" s="10">
+        <v>-3.2782694628944981E-2</v>
+      </c>
+      <c r="D63" s="10">
+        <v>0.61140881583395812</v>
+      </c>
+      <c r="E63" s="10">
+        <v>0.85720199084143156</v>
+      </c>
+      <c r="F63" s="10">
+        <v>0.61102059548167342</v>
+      </c>
+      <c r="G63" s="10">
+        <v>0.83583568339530101</v>
+      </c>
+      <c r="H63" s="10">
+        <v>0.15445616877731899</v>
+      </c>
+      <c r="I63" s="10">
+        <v>8.9896323472831163E-2</v>
+      </c>
+      <c r="J63" s="10">
+        <v>2.1197157911392539E-2</v>
+      </c>
+      <c r="K63" s="10">
+        <v>-2.2450150418724668E-3</v>
+      </c>
+      <c r="L63" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="10">
-        <v>0.71408893974753562</v>
-      </c>
-      <c r="C59" s="10">
-        <v>-0.10167092662206698</v>
-      </c>
-      <c r="D59" s="10">
-        <v>0.55495575040317713</v>
-      </c>
-      <c r="E59" s="10">
-        <v>0.82129332854745685</v>
-      </c>
-      <c r="F59" s="10">
-        <v>0.68453245198728596</v>
-      </c>
-      <c r="G59" s="10">
-        <v>0.79501037651194828</v>
-      </c>
-      <c r="H59" s="10">
-        <v>-0.6368043517080505</v>
-      </c>
-      <c r="I59" s="10">
-        <v>0.24498554032443401</v>
-      </c>
-      <c r="J59" s="10">
-        <v>0.2535169855949545</v>
-      </c>
-      <c r="K59" s="10">
-        <v>-0.15669531674477302</v>
-      </c>
-      <c r="L59" s="10">
-        <v>40</v>
+      <c r="B64" s="10">
+        <v>0.71361409294516331</v>
+      </c>
+      <c r="C64" s="10">
+        <v>-0.10130139704160743</v>
+      </c>
+      <c r="D64" s="10">
+        <v>0.55674440593763952</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.82183365942939957</v>
+      </c>
+      <c r="F64" s="10">
+        <v>0.68019311480774436</v>
+      </c>
+      <c r="G64" s="10">
+        <v>0.79683835646676049</v>
+      </c>
+      <c r="H64" s="10">
+        <v>-0.61849866461049241</v>
+      </c>
+      <c r="I64" s="10">
+        <v>0.24053314422200295</v>
+      </c>
+      <c r="J64" s="10">
+        <v>0.24688417445741506</v>
+      </c>
+      <c r="K64" s="10">
+        <v>-0.1482279265727659</v>
+      </c>
+      <c r="L64" s="10">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/Final_winner_optimization.xlsx
+++ b/logs/final_winner_optimization/Final_winner_optimization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/final_winner_optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B00E18A-8DE8-4B35-BA93-E267AE6C2AEA}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583FBBC7-87CD-40A9-84EB-414253B05403}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -689,16 +689,24 @@
       <sharedItems longText="1"/>
     </cacheField>
     <cacheField name="head_number" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="3"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="3" count="1">
+        <n v="3"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="encoding" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="compact"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="ansatz" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="entangle" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="full"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
       <sharedItems/>
@@ -909,10 +917,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -986,10 +994,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1063,10 +1071,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1140,10 +1148,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1217,10 +1225,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1294,10 +1302,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1371,10 +1379,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1448,10 +1456,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1525,10 +1533,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1602,10 +1610,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1679,10 +1687,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1756,10 +1764,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1833,10 +1841,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1910,10 +1918,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -1987,10 +1995,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2064,10 +2072,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2141,10 +2149,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2218,10 +2226,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2295,10 +2303,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2372,10 +2380,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2449,10 +2457,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2526,10 +2534,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2603,10 +2611,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2680,10 +2688,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2757,10 +2765,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2834,10 +2842,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2911,10 +2919,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -2988,10 +2996,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3065,10 +3073,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3142,10 +3150,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3219,10 +3227,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3296,10 +3304,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3373,10 +3381,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3450,10 +3458,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3527,10 +3535,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3604,10 +3612,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3681,10 +3689,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3758,10 +3766,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3835,10 +3843,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3912,10 +3920,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -3989,10 +3997,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -4066,10 +4074,10 @@
     <s v="false"/>
     <s v="multihead"/>
     <s v="[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
-    <n v="3"/>
-    <s v="compact"/>
-    <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
-    <s v="full"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="[2, 3, 2]"/>
     <s v="[[0, 1, 2], [0, 1, 2], [0, 1, -1]]"/>
     <s v="false"/>
@@ -4129,7 +4137,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24326305-70A8-4C78-9FE9-6DC3DEA8AA33}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24326305-70A8-4C78-9FE9-6DC3DEA8AA33}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:L64" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
@@ -4158,10 +4166,30 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14505,18 +14533,19 @@
   <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
